--- a/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -13,11 +13,9 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="SIM_業界資料の金額" sheetId="1" r:id="rId1"/>
-    <sheet name="比較_業界資料の金額" sheetId="2" r:id="rId2"/>
-    <sheet name="SIM_AIの金額" sheetId="3" r:id="rId100"/>
-    <sheet name="比較_AIの金額" sheetId="4" r:id="rId101"/>
-    <sheet name="SIM考え方" sheetId="5" r:id="rId3"/>
+    <sheet name="SIM_竹（コンサル基本）" sheetId="1" r:id="rId1"/>
+    <sheet name="SIM_比較" sheetId="2" r:id="rId2"/>
+    <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
   <extLst>
@@ -5373,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="51">
-        <v>100000</v>
+        <v>300000</v>
       </c>
       <c r="E69" s="28">
         <v>200000</v>
@@ -5395,7 +5393,7 @@
       </c>
       <c r="N69" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）月20万円。初期は業界資料の費用プラン：A コンサル基本 初期10万円〜</t>
+          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）月20万円。初期は初期30万円</t>
         </is>
       </c>
       <c r="O69" s="5" t="s">
@@ -5680,13 +5678,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="86">
-        <f>+'SIM_業界資料の金額'!D24</f>
+        <f>+'SIM_竹（コンサル基本）'!D24</f>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM_業界資料の金額'!G51</f>
+        <f>+'SIM_竹（コンサル基本）'!G51</f>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM_業界資料の金額'!J51</f>
+        <f>+'SIM_竹（コンサル基本）'!J51</f>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5696,13 +5694,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="86">
-        <f>+'SIM_業界資料の金額'!D25</f>
+        <f>+'SIM_竹（コンサル基本）'!D25</f>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM_業界資料の金額'!G61</f>
+        <f>+'SIM_竹（コンサル基本）'!G61</f>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM_業界資料の金額'!J61</f>
+        <f>+'SIM_竹（コンサル基本）'!J61</f>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5712,13 +5710,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM_業界資料の金額'!D28</f>
+        <f>+'SIM_竹（コンサル基本）'!D28</f>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM_業界資料の金額'!G28</f>
+        <f>+'SIM_竹（コンサル基本）'!G28</f>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM_業界資料の金額'!J28</f>
+        <f>+'SIM_竹（コンサル基本）'!J28</f>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5728,13 +5726,13 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM_業界資料の金額'!D27</f>
+        <f>+'SIM_竹（コンサル基本）'!D27</f>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM_業界資料の金額'!G27</f>
+        <f>+'SIM_竹（コンサル基本）'!G27</f>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM_業界資料の金額'!J27</f>
+        <f>+'SIM_竹（コンサル基本）'!J27</f>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5744,13 +5742,13 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM_業界資料の金額'!D29</f>
+        <f>+'SIM_竹（コンサル基本）'!D29</f>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM_業界資料の金額'!G29</f>
+        <f>+'SIM_竹（コンサル基本）'!G29</f>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM_業界資料の金額'!J29</f>
+        <f>+'SIM_竹（コンサル基本）'!J29</f>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5768,13 +5766,13 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM_業界資料の金額'!D34</f>
+        <f>+'SIM_竹（コンサル基本）'!D34</f>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM_業界資料の金額'!G34</f>
+        <f>+'SIM_竹（コンサル基本）'!G34</f>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM_業界資料の金額'!J34</f>
+        <f>+'SIM_竹（コンサル基本）'!J34</f>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5784,13 +5782,13 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM_業界資料の金額'!D35</f>
+        <f>+'SIM_竹（コンサル基本）'!D35</f>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM_業界資料の金額'!G35</f>
+        <f>+'SIM_竹（コンサル基本）'!G35</f>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM_業界資料の金額'!J35</f>
+        <f>+'SIM_竹（コンサル基本）'!J35</f>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5845,13 +5843,13 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM_業界資料の金額'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM_業界資料の金額'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM_業界資料の金額'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5893,13 +5891,13 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM_業界資料の金額'!D36</f>
+        <f>+'SIM_竹（コンサル基本）'!D36</f>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM_業界資料の金額'!G36</f>
+        <f>+'SIM_竹（コンサル基本）'!G36</f>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM_業界資料の金額'!J36</f>
+        <f>+'SIM_竹（コンサル基本）'!J36</f>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5932,13 +5930,13 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM_業界資料の金額'!D37</f>
+        <f>+'SIM_竹（コンサル基本）'!D37</f>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM_業界資料の金額'!G37</f>
+        <f>+'SIM_竹（コンサル基本）'!G37</f>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM_業界資料の金額'!J37</f>
+        <f>+'SIM_竹（コンサル基本）'!J37</f>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5971,13 +5969,13 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM_業界資料の金額'!D38</f>
+        <f>+'SIM_竹（コンサル基本）'!D38</f>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM_業界資料の金額'!G38</f>
+        <f>+'SIM_竹（コンサル基本）'!G38</f>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM_業界資料の金額'!J38</f>
+        <f>+'SIM_竹（コンサル基本）'!J38</f>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5994,13 +5992,13 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM_業界資料の金額'!D39</f>
+        <f>+'SIM_竹（コンサル基本）'!D39</f>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM_業界資料の金額'!G39</f>
+        <f>+'SIM_竹（コンサル基本）'!G39</f>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM_業界資料の金額'!J39</f>
+        <f>+'SIM_竹（コンサル基本）'!J39</f>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -6083,13 +6081,13 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM_業界資料の金額'!E68+C29*C30</f>
+        <f>+'SIM_竹（コンサル基本）'!E68+C29*C30</f>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM_業界資料の金額'!G68+D29*D30</f>
+        <f>+'SIM_竹（コンサル基本）'!G68+D29*D30</f>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM_業界資料の金額'!J68+E29*E30</f>
+        <f>+'SIM_竹（コンサル基本）'!J68+E29*E30</f>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -6570,2993 +6568,6 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="F42" s="61"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB115AE4-4B7C-5822-BE76-BF90E1DC773D}">
-  <dimension ref="A2:Z76"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="19.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="29.25" style="5" customWidth="1"/>
-    <col min="3" max="12" width="20" style="5" customWidth="1"/>
-    <col min="13" max="13" width="2.625" style="5" customWidth="1"/>
-    <col min="14" max="14" width="44.5" style="69" customWidth="1"/>
-    <col min="15" max="17" width="24.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="2.875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="12.125" style="5" customWidth="1"/>
-    <col min="20" max="20" width="2.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.125" style="5" customWidth="1"/>
-    <col min="22" max="22" width="2.875" style="5" customWidth="1"/>
-    <col min="23" max="23" width="12.125" style="5" customWidth="1"/>
-    <col min="24" max="24" width="2.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.125" style="5" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A2" s="156" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="157">
-        <v>46314</v>
-      </c>
-    </row>
-    <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">清水グループ御中_LINEOA施策提案【SIM】（離脱防止＋サイトのLINEボタン＋サンクスLINE誘導）</t>
-        </is>
-      </c>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-      <c r="Q4" s="55"/>
-      <c r="R4" s="55"/>
-      <c r="S4" s="55"/>
-      <c r="T4" s="55"/>
-      <c r="U4" s="55"/>
-      <c r="V4" s="55"/>
-      <c r="W4" s="55"/>
-      <c r="X4" s="55"/>
-      <c r="Y4" s="55"/>
-    </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.4">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="N5" s="55" t="s">
-        <v>189</v>
-      </c>
-      <c r="O5" s="55"/>
-      <c r="P5" s="55"/>
-      <c r="Q5" s="55"/>
-      <c r="R5" s="55"/>
-      <c r="S5" s="55"/>
-      <c r="T5" s="55"/>
-      <c r="U5" s="55"/>
-      <c r="V5" s="55"/>
-      <c r="W5" s="55"/>
-      <c r="X5" s="55"/>
-      <c r="Y5" s="55"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="N6" s="55"/>
-      <c r="O6" s="55"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="55"/>
-      <c r="R6" s="55"/>
-      <c r="S6" s="55"/>
-      <c r="T6" s="55"/>
-      <c r="U6" s="55"/>
-      <c r="V6" s="55"/>
-      <c r="W6" s="55"/>
-      <c r="X6" s="55"/>
-      <c r="Y6" s="55"/>
-    </row>
-    <row r="7" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="130" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募</t>
-        </is>
-      </c>
-      <c r="D8" s="33">
-        <v>0</v>
-      </c>
-      <c r="G8" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトUU</t>
-        </is>
-      </c>
-      <c r="H8" s="144">
-        <v>8947</v>
-      </c>
-      <c r="I8" s="145"/>
-      <c r="J8" s="145" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="152">
-        <v>0</v>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①応募：LINEのリンクからの応募だけ。サンクスLINEで友だちになった方（応募済み）の応募は数えない</t>
-        </is>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="131"/>
-      <c r="B9" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-      <c r="G9" s="146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">うち広告</t>
-        </is>
-      </c>
-      <c r="H9" s="147">
-        <v>0</v>
-      </c>
-      <c r="I9" s="148"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="140"/>
-      <c r="N9" s="155" t="s">
-        <v>127</v>
-      </c>
-      <c r="O9" s="153" t="s">
-        <v>187</v>
-      </c>
-      <c r="P9" s="154" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A10" s="130" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="G10" s="146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募（サイト・仮に）</t>
-        </is>
-      </c>
-      <c r="H10" s="147">
-        <v>134</v>
-      </c>
-      <c r="I10" s="148" t="s">
-        <v>186</v>
-      </c>
-      <c r="J10" s="139"/>
-      <c r="K10" s="140"/>
-      <c r="N10" s="155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトからの応募は与件に無いので、仮にUUの1.5%（月134件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="131"/>
-      <c r="B11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D11" s="33">
-        <v>0</v>
-      </c>
-      <c r="G11" s="149" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="150">
-        <v>0</v>
-      </c>
-      <c r="I11" s="151" t="s">
-        <v>185</v>
-      </c>
-      <c r="J11" s="141"/>
-      <c r="K11" s="142"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="O12" s="55" t="s">
-        <v>79</v>
-      </c>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="55"/>
-      <c r="S12" s="55"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="55"/>
-      <c r="V12" s="55"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A13" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="132"/>
-      <c r="C13" s="95"/>
-      <c r="D13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1か月目</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2か月目</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3か月目</t>
-        </is>
-      </c>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4か月目</t>
-        </is>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5か月目</t>
-        </is>
-      </c>
-      <c r="J13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6か月目</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N13" s="71" t="s">
-        <v>142</v>
-      </c>
-      <c r="O13" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-    </row>
-    <row r="14" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="99"/>
-      <c r="D14" s="42">
-        <f>+H8</f>
-      </c>
-      <c r="E14" s="43">
-        <f>+D14</f>
-      </c>
-      <c r="F14" s="43">
-        <f t="shared" ref="F14:J14" si="0">+E14</f>
-      </c>
-      <c r="G14" s="43">
-        <f t="shared" si="0"/>
-      </c>
-      <c r="H14" s="43">
-        <f t="shared" si="0"/>
-      </c>
-      <c r="I14" s="43">
-        <f t="shared" si="0"/>
-      </c>
-      <c r="J14" s="43">
-        <f t="shared" si="0"/>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="7"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">求人サイトの月間UU 8,947（与件）。6か月同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="134"/>
-      <c r="B15" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="99"/>
-      <c r="D15" s="42">
-        <f t="shared" ref="D15" si="1">+H9</f>
-      </c>
-      <c r="E15" s="43">
-        <f t="shared" ref="E15:J16" si="2">+D15</f>
-      </c>
-      <c r="F15" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="G15" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="H15" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="I15" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="J15" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="7"/>
-      <c r="N15" s="69" t="s">
-        <v>193</v>
-      </c>
-      <c r="O15" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" s="79">
-        <v>5.0000000000000001E-3</v>
-      </c>
-      <c r="S15" s="29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A16" s="135"/>
-      <c r="B16" s="20" t="s">
-        <v>180</v>
-      </c>
-      <c r="C16" s="99"/>
-      <c r="D16" s="42">
-        <f>H10</f>
-      </c>
-      <c r="E16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="F16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="G16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="H16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="I16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="J16" s="43">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="7"/>
-      <c r="N16" s="69" t="s">
-        <v>192</v>
-      </c>
-      <c r="O16" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="P16" s="79">
-        <v>2.5000000000000001E-3</v>
-      </c>
-      <c r="S16" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A17" s="133" t="s">
-        <v>3</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="100"/>
-      <c r="D17" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J17" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L17" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="W17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z17" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A18" s="134"/>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
-      </c>
-      <c r="C18" s="100"/>
-      <c r="D18" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="K18" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="N18" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="O18" s="22" t="s">
-        <v>40</v>
-      </c>
-      <c r="P18" s="78">
-        <v>0.65</v>
-      </c>
-      <c r="S18" s="5">
-        <v>0</v>
-      </c>
-      <c r="T18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="U18" s="34">
-        <v>200000</v>
-      </c>
-      <c r="W18" s="5">
-        <v>0</v>
-      </c>
-      <c r="X18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y18" s="34">
-        <v>600000</v>
-      </c>
-      <c r="Z18" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A19" s="134"/>
-      <c r="B19" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="C19" s="100"/>
-      <c r="D19" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="H19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="57" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" s="14"/>
-      <c r="L19" s="9"/>
-      <c r="N19" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="O19" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="P19" s="78">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="S19" s="34">
-        <v>200000</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="U19" s="34">
-        <v>15000000</v>
-      </c>
-      <c r="W19" s="34">
-        <v>600000</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="Y19" s="34">
-        <f>+U19*2.5</f>
-      </c>
-      <c r="Z19" s="35">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A20" s="134"/>
-      <c r="B20" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="C20" s="100"/>
-      <c r="D20" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J20" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" s="14"/>
-      <c r="L20" s="9"/>
-      <c r="S20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="W20" s="34"/>
-      <c r="Y20" s="34"/>
-      <c r="Z20" s="35"/>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A21" s="135"/>
-      <c r="B21" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C21" s="100"/>
-      <c r="D21" s="58" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="J21" s="57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K21" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="L21" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="O21" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="P21" s="26"/>
-      <c r="S21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="W21" s="34"/>
-      <c r="Y21" s="34"/>
-      <c r="Z21" s="35"/>
-    </row>
-    <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="136" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="17"/>
-      <c r="D22" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0</v>
-      </c>
-      <c r="H22" s="63">
-        <v>0</v>
-      </c>
-      <c r="I22" s="63">
-        <v>0</v>
-      </c>
-      <c r="J22" s="63">
-        <v>0</v>
-      </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="7"/>
-      <c r="N22" s="69" t="s">
-        <v>138</v>
-      </c>
-      <c r="O22" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="P22" s="24">
-        <v>0.78</v>
-      </c>
-      <c r="S22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="W22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="35"/>
-    </row>
-    <row r="23" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A23" s="134"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
-      </c>
-      <c r="C23" s="17"/>
-      <c r="D23" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="46">
-        <f>IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="F23" s="46">
-        <f>IF(F18=FALSE,0,F14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="G23" s="63">
-        <f>IF(G18=FALSE,0,G14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="H23" s="63">
-        <f>IF(H18=FALSE,0,H14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="I23" s="63">
-        <f>IF(I18=FALSE,0,I14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="J23" s="63">
-        <f>IF(J18=FALSE,0,J14*$P$18*0.125*0.125)</f>
-      </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="7"/>
-      <c r="N23" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ＝UU×表示65%×クリック12.5%×追加12.5%（定義テキストの係数）</t>
-        </is>
-      </c>
-      <c r="O23" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="P23" s="24">
-        <v>0.1</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="S23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="W23" s="34"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="35"/>
-    </row>
-    <row r="24" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A24" s="134"/>
-      <c r="B24" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="46">
-        <f>IF(E19=FALSE,0,E16*0.8*0.45)</f>
-      </c>
-      <c r="F24" s="63">
-        <f>IF(F19=FALSE,0,F16*0.8*0.45)</f>
-      </c>
-      <c r="G24" s="63">
-        <f>IF(G19=FALSE,0,G16*0.8*0.45)</f>
-      </c>
-      <c r="H24" s="63">
-        <f>IF(H19=FALSE,0,H16*0.8*0.45)</f>
-      </c>
-      <c r="I24" s="63">
-        <f>IF(I19=FALSE,0,I16*0.8*0.45)</f>
-      </c>
-      <c r="J24" s="63">
-        <f>IF(J19=FALSE,0,J16*0.8*0.45)</f>
-      </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導＝応募×遷移80%×追加45%（定義テキストの係数）</t>
-        </is>
-      </c>
-      <c r="O24" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="P24" s="77">
-        <v>0.8</v>
-      </c>
-      <c r="Q24" s="70">
-        <v>0.8</v>
-      </c>
-      <c r="S24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="W24" s="34"/>
-      <c r="Y24" s="34"/>
-      <c r="Z24" s="35"/>
-    </row>
-    <row r="25" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="135"/>
-      <c r="B25" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="17"/>
-      <c r="D25" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="46">
-        <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-      </c>
-      <c r="F25" s="46">
-        <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
-      </c>
-      <c r="G25" s="46">
-        <f t="shared" si="5"/>
-      </c>
-      <c r="H25" s="46">
-        <f t="shared" si="5"/>
-      </c>
-      <c r="I25" s="46">
-        <f t="shared" si="5"/>
-      </c>
-      <c r="J25" s="46">
-        <f t="shared" si="5"/>
-      </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="7"/>
-      <c r="N25" s="69" t="s">
-        <v>141</v>
-      </c>
-      <c r="O25" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="P25" s="26"/>
-      <c r="S25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="W25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="35"/>
-    </row>
-    <row r="26" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A26" s="120" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="121"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="46">
-        <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
-      </c>
-      <c r="F26" s="46">
-        <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-      </c>
-      <c r="G26" s="46">
-        <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
-      </c>
-      <c r="H26" s="46">
-        <f t="shared" si="6"/>
-      </c>
-      <c r="I26" s="46">
-        <f t="shared" si="6"/>
-      </c>
-      <c r="J26" s="46">
-        <f t="shared" si="6"/>
-      </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="7"/>
-      <c r="N26" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止＋サンクスLINE誘導</t>
-        </is>
-      </c>
-      <c r="O26" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="P26" s="24">
-        <v>0.72499999999999998</v>
-      </c>
-      <c r="S26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="W26" s="34"/>
-      <c r="Y26" s="34"/>
-      <c r="Z26" s="35"/>
-    </row>
-    <row r="27" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A27" s="120" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="121"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="107">
-        <v>0</v>
-      </c>
-      <c r="E27" s="47">
-        <v>0.38</v>
-      </c>
-      <c r="F27" s="47">
-        <v>0.384</v>
-      </c>
-      <c r="G27" s="47">
-        <v>0.388</v>
-      </c>
-      <c r="H27" s="47">
-        <v>0.392</v>
-      </c>
-      <c r="I27" s="47">
-        <v>0.396</v>
-      </c>
-      <c r="J27" s="47">
-        <v>0.4</v>
-      </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="7"/>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ブロック率：求人は用が済むとブロックされやすいので、38%から少しずつ上がる想定</t>
-        </is>
-      </c>
-      <c r="O27" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="P27" s="24">
-        <v>0.12</v>
-      </c>
-      <c r="Q27" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="S27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="35"/>
-    </row>
-    <row r="28" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A28" s="137" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="138"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="106">
-        <v>0</v>
-      </c>
-      <c r="E28" s="49">
-        <f>+D28+E26</f>
-      </c>
-      <c r="F28" s="49">
-        <f t="shared" ref="F28:J28" si="8">+E28+F26</f>
-      </c>
-      <c r="G28" s="49">
-        <f t="shared" si="8"/>
-      </c>
-      <c r="H28" s="49">
-        <f t="shared" si="8"/>
-      </c>
-      <c r="I28" s="49">
-        <f t="shared" si="8"/>
-      </c>
-      <c r="J28" s="49">
-        <f t="shared" si="8"/>
-      </c>
-      <c r="K28" s="12"/>
-      <c r="L28" s="7"/>
-      <c r="O28" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="P28" s="77">
-        <v>0.2</v>
-      </c>
-      <c r="Q28" s="70">
-        <v>0.8</v>
-      </c>
-      <c r="S28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="W28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="35"/>
-    </row>
-    <row r="29" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A29" s="126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="127"/>
-      <c r="C29" s="102"/>
-      <c r="D29" s="108">
-        <f>+D28*(1-D27)</f>
-      </c>
-      <c r="E29" s="50">
-        <f>+E28*(1-E27)</f>
-      </c>
-      <c r="F29" s="50">
-        <f t="shared" ref="F29:J29" si="9">+F28*(1-F27)</f>
-      </c>
-      <c r="G29" s="50">
-        <f t="shared" si="9"/>
-      </c>
-      <c r="H29" s="50">
-        <f t="shared" si="9"/>
-      </c>
-      <c r="I29" s="50">
-        <f t="shared" si="9"/>
-      </c>
-      <c r="J29" s="50">
-        <f t="shared" si="9"/>
-      </c>
-      <c r="K29" s="12"/>
-      <c r="L29" s="7"/>
-      <c r="N29" s="69" t="s">
-        <v>159</v>
-      </c>
-      <c r="S29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="W29" s="34"/>
-      <c r="Y29" s="34"/>
-      <c r="Z29" s="35"/>
-    </row>
-    <row r="30" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A30" s="124" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="125"/>
-      <c r="C30" s="30"/>
-      <c r="D30" s="48">
-        <v>0</v>
-      </c>
-      <c r="E30" s="45">
-        <v>3</v>
-      </c>
-      <c r="F30" s="45">
-        <v>3</v>
-      </c>
-      <c r="G30" s="45">
-        <v>3</v>
-      </c>
-      <c r="H30" s="45">
-        <v>3</v>
-      </c>
-      <c r="I30" s="45">
-        <v>3</v>
-      </c>
-      <c r="J30" s="45">
-        <v>3</v>
-      </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="7"/>
-      <c r="N30" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">企画配信 月3回（業界資料の竹＝コンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
-        </is>
-      </c>
-      <c r="O30" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="P30" s="76"/>
-      <c r="S30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="W30" s="34"/>
-      <c r="Y30" s="34"/>
-      <c r="Z30" s="35"/>
-    </row>
-    <row r="31" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A31" s="120" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="121"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="108">
-        <f>+D30*D29*0.41*0.07</f>
-      </c>
-      <c r="E31" s="63">
-        <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
-      </c>
-      <c r="F31" s="63">
-        <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
-      </c>
-      <c r="G31" s="63">
-        <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
-      </c>
-      <c r="H31" s="63">
-        <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-      </c>
-      <c r="I31" s="63">
-        <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-      </c>
-      <c r="J31" s="63">
-        <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
-      </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="7"/>
-      <c r="S31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="W31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="35"/>
-    </row>
-    <row r="32" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A32" s="124" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="125"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="48">
-        <v>0</v>
-      </c>
-      <c r="E32" s="45">
-        <v>3</v>
-      </c>
-      <c r="F32" s="45">
-        <v>3</v>
-      </c>
-      <c r="G32" s="45">
-        <v>3</v>
-      </c>
-      <c r="H32" s="45">
-        <v>3</v>
-      </c>
-      <c r="I32" s="45">
-        <v>3</v>
-      </c>
-      <c r="J32" s="45">
-        <v>3</v>
-      </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="7"/>
-      <c r="N32" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ステップ配信3通（友だち追加の翌日以降。職種ごとに中身を分ける）</t>
-        </is>
-      </c>
-      <c r="O32" s="17" t="s">
-        <v>146</v>
-      </c>
-      <c r="P32" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q32" s="73">
-        <f>+IF(P32=TRUE,1.1,0.95)</f>
-      </c>
-      <c r="S32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="W32" s="34"/>
-      <c r="Z32" s="35"/>
-    </row>
-    <row r="33" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A33" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="121"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="44">
-        <v>0</v>
-      </c>
-      <c r="E33" s="63">
-        <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
-      </c>
-      <c r="F33" s="63">
-        <f t="shared" ref="F33:G33" si="10">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
-      </c>
-      <c r="G33" s="63">
-        <f t="shared" si="10"/>
-      </c>
-      <c r="H33" s="63">
-        <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-      </c>
-      <c r="I33" s="63">
-        <f t="shared" ref="I33:J33" si="11">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
-      </c>
-      <c r="J33" s="63">
-        <f t="shared" si="11"/>
-      </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="7"/>
-      <c r="O33" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="P33" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q33" s="73">
-        <f t="shared" ref="Q33:Q35" si="12">+IF(P33=TRUE,1.1,0.95)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A34" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="127"/>
-      <c r="C34" s="102"/>
-      <c r="D34" s="108">
-        <f>+D29*D30</f>
-      </c>
-      <c r="E34" s="46">
-        <f>+E29*E30*$P$24+E29*E32*$P$28</f>
-      </c>
-      <c r="F34" s="46">
-        <f>+F29*F30*$P$24+F29*F32*$P$28</f>
-      </c>
-      <c r="G34" s="46">
-        <f>+G29*G30*$P$24+G29*G32*$P$28</f>
-      </c>
-      <c r="H34" s="46">
-        <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
-      </c>
-      <c r="I34" s="46">
-        <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
-      </c>
-      <c r="J34" s="46">
-        <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
-      </c>
-      <c r="K34" s="11"/>
-      <c r="L34" s="7"/>
-      <c r="O34" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="P34" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q34" s="73">
-        <f t="shared" si="12"/>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A35" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="127"/>
-      <c r="C35" s="102"/>
-      <c r="D35" s="109">
-        <f>+D31*1.02</f>
-      </c>
-      <c r="E35" s="50">
-        <f>+E31+E33+1.05*(E31+E33)</f>
-      </c>
-      <c r="F35" s="50">
-        <f t="shared" ref="F35:J35" si="13">+F31+F33+1.05*(F31+F33)</f>
-      </c>
-      <c r="G35" s="50">
-        <f t="shared" si="13"/>
-      </c>
-      <c r="H35" s="50">
-        <f t="shared" si="13"/>
-      </c>
-      <c r="I35" s="50">
-        <f t="shared" si="13"/>
-      </c>
-      <c r="J35" s="50">
-        <f t="shared" si="13"/>
-      </c>
-      <c r="K35" s="11"/>
-      <c r="L35" s="7"/>
-      <c r="O35" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="P35" s="75" t="b">
-        <v>1</v>
-      </c>
-      <c r="Q35" s="73">
-        <f t="shared" si="12"/>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A36" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="6">
-        <f>+C8</f>
-      </c>
-      <c r="C36" s="6"/>
-      <c r="D36" s="11">
-        <v>0</v>
-      </c>
-      <c r="E36" s="111">
-        <v>1</v>
-      </c>
-      <c r="F36" s="111">
-        <v>1</v>
-      </c>
-      <c r="G36" s="111">
-        <v>2</v>
-      </c>
-      <c r="H36" s="111">
-        <v>2</v>
-      </c>
-      <c r="I36" s="111">
-        <v>3</v>
-      </c>
-      <c r="J36" s="111">
-        <v>3</v>
-      </c>
-      <c r="K36" s="115">
-        <f>SUM(E36:J36)</f>
-      </c>
-      <c r="L36" s="7"/>
-      <c r="N36" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募：クリックの0.3〜1.0%前後</t>
-        </is>
-      </c>
-      <c r="O36" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="P36" s="74">
-        <f>1*(Q32*Q33*Q34*Q35)</f>
-      </c>
-      <c r="Q36" s="73"/>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A37" s="129"/>
-      <c r="B37" s="6">
-        <f>+C9</f>
-      </c>
-      <c r="C37" s="6"/>
-      <c r="D37" s="11">
-        <v>0</v>
-      </c>
-      <c r="E37" s="111">
-        <v>0</v>
-      </c>
-      <c r="F37" s="111">
-        <v>0</v>
-      </c>
-      <c r="G37" s="111">
-        <v>0</v>
-      </c>
-      <c r="H37" s="111">
-        <v>0</v>
-      </c>
-      <c r="I37" s="111">
-        <v>0</v>
-      </c>
-      <c r="J37" s="111">
-        <v>0</v>
-      </c>
-      <c r="K37" s="115">
-        <f>SUM(E37:J37)</f>
-      </c>
-      <c r="L37" s="7"/>
-      <c r="N37" s="69" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A38" s="128" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="6">
-        <f>+C10</f>
-      </c>
-      <c r="C38" s="6"/>
-      <c r="D38" s="11">
-        <v>0</v>
-      </c>
-      <c r="E38" s="111">
-        <v>0</v>
-      </c>
-      <c r="F38" s="111">
-        <v>0</v>
-      </c>
-      <c r="G38" s="111">
-        <v>0</v>
-      </c>
-      <c r="H38" s="111">
-        <v>0</v>
-      </c>
-      <c r="I38" s="111">
-        <v>0</v>
-      </c>
-      <c r="J38" s="111">
-        <v>0</v>
-      </c>
-      <c r="K38" s="115">
-        <f>SUM(E38:J38)</f>
-      </c>
-      <c r="L38" s="7"/>
-      <c r="N38" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="O38" s="21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A39" s="129"/>
-      <c r="B39" s="6">
-        <f>+C11</f>
-      </c>
-      <c r="C39" s="6"/>
-      <c r="D39" s="11">
-        <v>0</v>
-      </c>
-      <c r="E39" s="111">
-        <v>0</v>
-      </c>
-      <c r="F39" s="111">
-        <v>0</v>
-      </c>
-      <c r="G39" s="111">
-        <v>0</v>
-      </c>
-      <c r="H39" s="111">
-        <v>0</v>
-      </c>
-      <c r="I39" s="111">
-        <v>0</v>
-      </c>
-      <c r="J39" s="111">
-        <v>0</v>
-      </c>
-      <c r="K39" s="115">
-        <f>SUM(E39:J39)</f>
-      </c>
-      <c r="L39" s="7"/>
-      <c r="N39" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="O39" s="21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A40" s="122" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="123"/>
-      <c r="C40" s="97"/>
-      <c r="D40" s="11">
-        <f t="shared" ref="D40:J40" si="14">+SUM(D36:D39)</f>
-      </c>
-      <c r="E40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="F40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="G40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="H40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="I40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="J40" s="10">
-        <f t="shared" si="14"/>
-      </c>
-      <c r="K40" s="115">
-        <f>SUM(E40:J40)</f>
-      </c>
-      <c r="L40" s="7"/>
-      <c r="O40" s="17"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="B41" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="18">
-        <f t="shared" ref="D41" si="15">+IFERROR(D40/D35,0)</f>
-      </c>
-      <c r="E41" s="18">
-        <f>+IFERROR(E40/E35,0)</f>
-      </c>
-      <c r="F41" s="18">
-        <f t="shared" ref="F41:J41" si="16">+IFERROR(F40/F35,0)</f>
-      </c>
-      <c r="G41" s="18">
-        <f t="shared" si="16"/>
-      </c>
-      <c r="H41" s="18">
-        <f t="shared" si="16"/>
-      </c>
-      <c r="I41" s="18">
-        <f t="shared" si="16"/>
-      </c>
-      <c r="J41" s="18">
-        <f t="shared" si="16"/>
-      </c>
-      <c r="N41" s="69" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="B42" s="29"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="116"/>
-      <c r="H42" s="116"/>
-      <c r="I42" s="116"/>
-      <c r="J42" s="116"/>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A43" s="29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A44" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="121"/>
-      <c r="C44" s="103"/>
-      <c r="D44" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E44" s="31">
-        <f>+E75*E76</f>
-      </c>
-      <c r="F44" s="31">
-        <f t="shared" ref="F44:J44" si="17">+F75*F76</f>
-      </c>
-      <c r="G44" s="31">
-        <f t="shared" si="17"/>
-      </c>
-      <c r="H44" s="31">
-        <f t="shared" si="17"/>
-      </c>
-      <c r="I44" s="31">
-        <f t="shared" si="17"/>
-      </c>
-      <c r="J44" s="31">
-        <f t="shared" si="17"/>
-      </c>
-      <c r="K44" s="11"/>
-      <c r="L44" s="7"/>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A45" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="121"/>
-      <c r="C45" s="104">
-        <f>+SUM(C65:C72)</f>
-      </c>
-      <c r="D45" s="80">
-        <f>+SUM(D65:D72)</f>
-      </c>
-      <c r="E45" s="27">
-        <f>SUM(E65:E69)+SUM(E71:E72)</f>
-      </c>
-      <c r="F45" s="27">
-        <f t="shared" ref="F45:J45" si="18">SUM(F65:F69)+SUM(F71:F72)</f>
-      </c>
-      <c r="G45" s="27">
-        <f t="shared" si="18"/>
-      </c>
-      <c r="H45" s="27">
-        <f t="shared" si="18"/>
-      </c>
-      <c r="I45" s="27">
-        <f t="shared" si="18"/>
-      </c>
-      <c r="J45" s="27">
-        <f t="shared" si="18"/>
-      </c>
-      <c r="K45" s="11"/>
-      <c r="L45" s="7"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A46" s="120" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="121"/>
-      <c r="C46" s="103"/>
-      <c r="D46" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E46" s="28">
-        <f>IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
-      </c>
-      <c r="F46" s="28">
-        <f>IFERROR(SUM(F65:F67)/(F28-E28),"-")</f>
-      </c>
-      <c r="G46" s="28">
-        <f>IFERROR(SUM(G65:G67)/(G28-F28),"-")</f>
-      </c>
-      <c r="H46" s="28">
-        <f>IFERROR(SUM(H65:H67)/(H28-G28),"-")</f>
-      </c>
-      <c r="I46" s="28">
-        <f>IFERROR(SUM(I65:I67)/(I28-H28),"-")</f>
-      </c>
-      <c r="J46" s="28">
-        <f>IFERROR(SUM(J65:J67)/(J28-I28),"-")</f>
-      </c>
-      <c r="K46" s="11"/>
-      <c r="L46" s="7"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A47" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="121"/>
-      <c r="C47" s="103"/>
-      <c r="D47" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E47" s="28">
-        <f t="shared" ref="E47:I47" si="20">+E51/E35</f>
-      </c>
-      <c r="F47" s="28">
-        <f t="shared" si="20"/>
-      </c>
-      <c r="G47" s="28">
-        <f t="shared" si="20"/>
-      </c>
-      <c r="H47" s="28">
-        <f t="shared" si="20"/>
-      </c>
-      <c r="I47" s="28">
-        <f t="shared" si="20"/>
-      </c>
-      <c r="J47" s="28">
-        <f>+J51/J35</f>
-      </c>
-      <c r="K47" s="11"/>
-      <c r="L47" s="7"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A48" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="121"/>
-      <c r="C48" s="103"/>
-      <c r="D48" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E48" s="32">
-        <f t="shared" ref="E48:J48" si="21">+SUM(E36:E39)/E35</f>
-      </c>
-      <c r="F48" s="32">
-        <f t="shared" si="21"/>
-      </c>
-      <c r="G48" s="32">
-        <f t="shared" si="21"/>
-      </c>
-      <c r="H48" s="32">
-        <f t="shared" si="21"/>
-      </c>
-      <c r="I48" s="32">
-        <f t="shared" si="21"/>
-      </c>
-      <c r="J48" s="32">
-        <f t="shared" si="21"/>
-      </c>
-      <c r="K48" s="11"/>
-      <c r="L48" s="7"/>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A49" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="B49" s="123"/>
-      <c r="C49" s="105"/>
-      <c r="D49" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E49" s="28">
-        <f>+IFERROR(E51/SUM(E36:E39),0)</f>
-      </c>
-      <c r="F49" s="28">
-        <f t="shared" ref="F49:J49" si="22">+IFERROR(F51/SUM(F36:F39),0)</f>
-      </c>
-      <c r="G49" s="28">
-        <f t="shared" si="22"/>
-      </c>
-      <c r="H49" s="28">
-        <f t="shared" si="22"/>
-      </c>
-      <c r="I49" s="28">
-        <f t="shared" si="22"/>
-      </c>
-      <c r="J49" s="28">
-        <f t="shared" si="22"/>
-      </c>
-      <c r="K49" s="11"/>
-      <c r="L49" s="7"/>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A50" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="123"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="64" t="s">
-        <v>23</v>
-      </c>
-      <c r="E50" s="65">
-        <f>+E36*$D$8+E38*$D$10</f>
-      </c>
-      <c r="F50" s="65">
-        <f t="shared" ref="F50:J50" si="23">+F36*$D$8+F38*$D$10</f>
-      </c>
-      <c r="G50" s="65">
-        <f t="shared" si="23"/>
-      </c>
-      <c r="H50" s="65">
-        <f t="shared" si="23"/>
-      </c>
-      <c r="I50" s="65">
-        <f t="shared" si="23"/>
-      </c>
-      <c r="J50" s="65">
-        <f t="shared" si="23"/>
-      </c>
-      <c r="K50" s="11"/>
-      <c r="L50" s="7"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A51" s="118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="119"/>
-      <c r="C51" s="110">
-        <f>+C45</f>
-      </c>
-      <c r="D51" s="40">
-        <f>+D45</f>
-      </c>
-      <c r="E51" s="40">
-        <f>SUM(E45,E50)+E44</f>
-      </c>
-      <c r="F51" s="40">
-        <f t="shared" ref="F51:I51" si="24">SUM(F45,F50)+F44</f>
-      </c>
-      <c r="G51" s="40">
-        <f t="shared" si="24"/>
-      </c>
-      <c r="H51" s="40">
-        <f t="shared" si="24"/>
-      </c>
-      <c r="I51" s="40">
-        <f t="shared" si="24"/>
-      </c>
-      <c r="J51" s="40">
-        <f>SUM(J45,J50)+J44</f>
-      </c>
-      <c r="K51" s="11"/>
-      <c r="L51" s="7"/>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A52" s="22"/>
-      <c r="B52" s="22"/>
-      <c r="C52" s="22"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="37"/>
-    </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="121"/>
-      <c r="C54" s="96"/>
-      <c r="D54" s="28">
-        <f>+D75*D76</f>
-      </c>
-      <c r="E54" s="28">
-        <f t="shared" ref="E54:J54" si="25">+E75*E76</f>
-      </c>
-      <c r="F54" s="28">
-        <f t="shared" si="25"/>
-      </c>
-      <c r="G54" s="28">
-        <f t="shared" si="25"/>
-      </c>
-      <c r="H54" s="28">
-        <f t="shared" si="25"/>
-      </c>
-      <c r="I54" s="28">
-        <f t="shared" si="25"/>
-      </c>
-      <c r="J54" s="28">
-        <f t="shared" si="25"/>
-      </c>
-      <c r="K54" s="11"/>
-      <c r="L54" s="7"/>
-    </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" s="121"/>
-      <c r="C55" s="96"/>
-      <c r="D55" s="27">
-        <f>+SUM(D65:D72)</f>
-      </c>
-      <c r="E55" s="27">
-        <f>SUM(E65:E72)+E54</f>
-      </c>
-      <c r="F55" s="27">
-        <f t="shared" ref="F55:J55" si="26">SUM(F65:F72)+F54</f>
-      </c>
-      <c r="G55" s="27">
-        <f t="shared" si="26"/>
-      </c>
-      <c r="H55" s="27">
-        <f t="shared" si="26"/>
-      </c>
-      <c r="I55" s="27">
-        <f t="shared" si="26"/>
-      </c>
-      <c r="J55" s="27">
-        <f t="shared" si="26"/>
-      </c>
-      <c r="K55" s="11"/>
-      <c r="L55" s="7"/>
-    </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="120" t="s">
-        <v>18</v>
-      </c>
-      <c r="B56" s="121"/>
-      <c r="C56" s="96"/>
-      <c r="D56" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E56" s="28">
-        <f>IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
-      </c>
-      <c r="F56" s="28">
-        <f>IFERROR(SUM(F65:F67)/(F28-E28),"-")</f>
-      </c>
-      <c r="G56" s="28">
-        <f>IFERROR(SUM(G65:G67)/(G28-F28),"-")</f>
-      </c>
-      <c r="H56" s="28">
-        <f>IFERROR(SUM(H65:H67)/(H28-G28),"-")</f>
-      </c>
-      <c r="I56" s="28">
-        <f>IFERROR(SUM(I65:I67)/(I28-H28),"-")</f>
-      </c>
-      <c r="J56" s="28">
-        <f>IFERROR(SUM(J65:J67)/(J28-I28),"-")</f>
-      </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="7"/>
-    </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="B57" s="121"/>
-      <c r="C57" s="96"/>
-      <c r="D57" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E57" s="28">
-        <f>+E61/E35</f>
-      </c>
-      <c r="F57" s="28">
-        <f t="shared" ref="F57:J57" si="28">+F61/F35</f>
-      </c>
-      <c r="G57" s="28">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="H57" s="28">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="I57" s="28">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="J57" s="28">
-        <f t="shared" si="28"/>
-      </c>
-      <c r="K57" s="11"/>
-      <c r="L57" s="7"/>
-    </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="B58" s="121"/>
-      <c r="C58" s="96"/>
-      <c r="D58" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E58" s="32">
-        <f t="shared" ref="E58:J58" si="29">+SUM(E36:E39)/E35</f>
-      </c>
-      <c r="F58" s="32">
-        <f t="shared" si="29"/>
-      </c>
-      <c r="G58" s="32">
-        <f t="shared" si="29"/>
-      </c>
-      <c r="H58" s="32">
-        <f t="shared" si="29"/>
-      </c>
-      <c r="I58" s="32">
-        <f t="shared" si="29"/>
-      </c>
-      <c r="J58" s="32">
-        <f t="shared" si="29"/>
-      </c>
-      <c r="K58" s="11"/>
-      <c r="L58" s="7"/>
-    </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="123"/>
-      <c r="C59" s="97"/>
-      <c r="D59" s="28"/>
-      <c r="E59" s="28">
-        <f>+IFERROR(E55/E40,0)</f>
-      </c>
-      <c r="F59" s="28">
-        <f t="shared" ref="F59:J59" si="30">+IFERROR(F55/F40,0)</f>
-      </c>
-      <c r="G59" s="28">
-        <f t="shared" si="30"/>
-      </c>
-      <c r="H59" s="28">
-        <f t="shared" si="30"/>
-      </c>
-      <c r="I59" s="28">
-        <f t="shared" si="30"/>
-      </c>
-      <c r="J59" s="28">
-        <f t="shared" si="30"/>
-      </c>
-      <c r="K59" s="11"/>
-      <c r="L59" s="7"/>
-    </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="B60" s="123"/>
-      <c r="C60" s="97"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="28"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="11"/>
-      <c r="L60" s="7"/>
-    </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B61" s="119"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="40">
-        <f>+D55</f>
-      </c>
-      <c r="E61" s="40">
-        <f>+SUM(E65:E72)+E54</f>
-      </c>
-      <c r="F61" s="40">
-        <f t="shared" ref="F61:J61" si="31">+SUM(F65:F72)+F54</f>
-      </c>
-      <c r="G61" s="40">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="H61" s="40">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="I61" s="40">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="J61" s="40">
-        <f t="shared" si="31"/>
-      </c>
-      <c r="K61" s="11"/>
-      <c r="L61" s="7"/>
-    </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.4"/>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="C64" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A65" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" s="90">
-        <v>0</v>
-      </c>
-      <c r="D65" s="51">
-        <v>0</v>
-      </c>
-      <c r="E65" s="28">
-        <v>0</v>
-      </c>
-      <c r="F65" s="28">
-        <v>0</v>
-      </c>
-      <c r="G65" s="28">
-        <v>0</v>
-      </c>
-      <c r="H65" s="28">
-        <v>0</v>
-      </c>
-      <c r="I65" s="28">
-        <v>0</v>
-      </c>
-      <c r="J65" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A66" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
-      </c>
-      <c r="C66" s="90">
-        <v>0</v>
-      </c>
-      <c r="D66" s="51">
-        <v>15000</v>
-      </c>
-      <c r="E66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="F66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="G66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="H66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="I66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="J66" s="28">
-        <v>30000</v>
-      </c>
-      <c r="N66" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導</t>
-        </is>
-      </c>
-      <c r="C67" s="90">
-        <v>0</v>
-      </c>
-      <c r="D67" s="51">
-        <v>150000</v>
-      </c>
-      <c r="E67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="F67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="G67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="H67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="I67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="J67" s="28">
-        <v>30000</v>
-      </c>
-      <c r="N67" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導：初期15万円・月3万円〜</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A68" s="15"/>
-      <c r="B68" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C68" s="90">
-        <v>0</v>
-      </c>
-      <c r="D68" s="51">
-        <v>30000</v>
-      </c>
-      <c r="E68" s="28">
-        <f t="shared" ref="E68:J68" si="33">IF(E34&lt;5000,5000,15000)</f>
-      </c>
-      <c r="F68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="G68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="H68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="I68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="J68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="N68" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">アカウント費：FMTの式（開設3万円）</t>
-        </is>
-      </c>
-      <c r="O68" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="P68" s="75">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A69" s="15"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）</t>
-        </is>
-      </c>
-      <c r="C69" s="90">
-        <v>0</v>
-      </c>
-      <c r="D69" s="51">
-        <v>300000</v>
-      </c>
-      <c r="E69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="F69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="G69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="H69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="I69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="J69" s="28">
-        <v>200000</v>
-      </c>
-      <c r="N69" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）月20万円。初期はAIの案：竹（A：コンサル基本）初期30万円</t>
-        </is>
-      </c>
-      <c r="O69" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A70" s="15"/>
-      <c r="B70" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="C70" s="90">
-        <v>0</v>
-      </c>
-      <c r="D70" s="51">
-        <v>0</v>
-      </c>
-      <c r="E70" s="28">
-        <v>0</v>
-      </c>
-      <c r="F70" s="28">
-        <v>0</v>
-      </c>
-      <c r="G70" s="28">
-        <v>0</v>
-      </c>
-      <c r="H70" s="28">
-        <v>0</v>
-      </c>
-      <c r="I70" s="28">
-        <v>0</v>
-      </c>
-      <c r="J70" s="28">
-        <v>0</v>
-      </c>
-      <c r="N70" s="69" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A71" s="15"/>
-      <c r="B71" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C71" s="90">
-        <v>0</v>
-      </c>
-      <c r="D71" s="51">
-        <v>0</v>
-      </c>
-      <c r="E71" s="28">
-        <v>0</v>
-      </c>
-      <c r="F71" s="28">
-        <v>0</v>
-      </c>
-      <c r="G71" s="28">
-        <v>0</v>
-      </c>
-      <c r="H71" s="28">
-        <v>0</v>
-      </c>
-      <c r="I71" s="28">
-        <v>0</v>
-      </c>
-      <c r="J71" s="28">
-        <v>0</v>
-      </c>
-      <c r="N71" s="69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A72" s="15"/>
-      <c r="B72" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="90">
-        <v>0</v>
-      </c>
-      <c r="D72" s="51">
-        <v>0</v>
-      </c>
-      <c r="E72" s="28">
-        <v>0</v>
-      </c>
-      <c r="F72" s="28">
-        <v>0</v>
-      </c>
-      <c r="G72" s="28">
-        <v>0</v>
-      </c>
-      <c r="H72" s="28">
-        <v>0</v>
-      </c>
-      <c r="I72" s="28">
-        <v>0</v>
-      </c>
-      <c r="J72" s="28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A73" s="15"/>
-      <c r="B73" s="112" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" s="113">
-        <v>0</v>
-      </c>
-      <c r="D73" s="114">
-        <f>SUM(D65:D72)</f>
-      </c>
-      <c r="E73" s="114">
-        <f>SUM(E65:E72)+E54</f>
-      </c>
-      <c r="F73" s="114">
-        <f>SUM(F65:F72)+F54</f>
-      </c>
-      <c r="G73" s="114">
-        <f>SUM(G65:G72)+G54</f>
-      </c>
-      <c r="H73" s="114">
-        <f>SUM(H65:H72)+H54</f>
-      </c>
-      <c r="I73" s="114">
-        <f>SUM(I65:I72)+I54</f>
-      </c>
-      <c r="J73" s="114">
-        <f>SUM(J65:J72)+J54</f>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="A74" s="15"/>
-      <c r="B74" s="15"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
-      <c r="G74" s="15"/>
-      <c r="H74" s="15"/>
-      <c r="I74" s="15"/>
-      <c r="J74" s="15"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B75" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="41">
-        <f t="shared" ref="D75:J75" si="40">+IF(D34&lt;30001,0,D34-30000)</f>
-      </c>
-      <c r="E75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="F75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="G75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="H75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="I75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-      <c r="J75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B76" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D76" s="5">
-        <f>+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="E76" s="5">
-        <f>+IF(E75&lt;=$U$18,$Z$18,IF(E75&lt;=$U$19,$Z$19,IF(E75&lt;=$U$20,$Z$20,IF(E75&lt;=$U$21,$Z$21,IF(E75&lt;=$U$22,$Z$22,IF(E75&lt;=$U$23,$Z$23,IF(E75&lt;=$U$24,$Z$24,IF(E75&lt;=$U$25,$Z$25,IF(E75&lt;=$U$26,$Z$26,IF(E75&lt;=$U$27,$Z$27,IF(E75&lt;=$U$28,$Z$28,IF(E75&lt;=$U$29,$Z$29,IF(E75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="F76" s="5">
-        <f>+IF(F75&lt;=$U$18,$Z$18,IF(F75&lt;=$U$19,$Z$19,IF(F75&lt;=$U$20,$Z$20,IF(F75&lt;=$U$21,$Z$21,IF(F75&lt;=$U$22,$Z$22,IF(F75&lt;=$U$23,$Z$23,IF(F75&lt;=$U$24,$Z$24,IF(F75&lt;=$U$25,$Z$25,IF(F75&lt;=$U$26,$Z$26,IF(F75&lt;=$U$27,$Z$27,IF(F75&lt;=$U$28,$Z$28,IF(F75&lt;=$U$29,$Z$29,IF(F75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="G76" s="5">
-        <f>+IF(G75&lt;=$U$18,$Z$18,IF(G75&lt;=$U$19,$Z$19,IF(G75&lt;=$U$20,$Z$20,IF(G75&lt;=$U$21,$Z$21,IF(G75&lt;=$U$22,$Z$22,IF(G75&lt;=$U$23,$Z$23,IF(G75&lt;=$U$24,$Z$24,IF(G75&lt;=$U$25,$Z$25,IF(G75&lt;=$U$26,$Z$26,IF(G75&lt;=$U$27,$Z$27,IF(G75&lt;=$U$28,$Z$28,IF(G75&lt;=$U$29,$Z$29,IF(G75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="H76" s="5">
-        <f>+IF(H75&lt;=$U$18,$Z$18,IF(H75&lt;=$U$19,$Z$19,IF(H75&lt;=$U$20,$Z$20,IF(H75&lt;=$U$21,$Z$21,IF(H75&lt;=$U$22,$Z$22,IF(H75&lt;=$U$23,$Z$23,IF(H75&lt;=$U$24,$Z$24,IF(H75&lt;=$U$25,$Z$25,IF(H75&lt;=$U$26,$Z$26,IF(H75&lt;=$U$27,$Z$27,IF(H75&lt;=$U$28,$Z$28,IF(H75&lt;=$U$29,$Z$29,IF(H75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="I76" s="5">
-        <f>+IF(I75&lt;=$U$18,$Z$18,IF(I75&lt;=$U$19,$Z$19,IF(I75&lt;=$U$20,$Z$20,IF(I75&lt;=$U$21,$Z$21,IF(I75&lt;=$U$22,$Z$22,IF(I75&lt;=$U$23,$Z$23,IF(I75&lt;=$U$24,$Z$24,IF(I75&lt;=$U$25,$Z$25,IF(I75&lt;=$U$26,$Z$26,IF(I75&lt;=$U$27,$Z$27,IF(I75&lt;=$U$28,$Z$28,IF(I75&lt;=$U$29,$Z$29,IF(I75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-      <c r="J76" s="5">
-        <f>+IF(J75&lt;=$U$18,$Z$18,IF(J75&lt;=$U$19,$Z$19,IF(J75&lt;=$U$20,$Z$20,IF(J75&lt;=$U$21,$Z$21,IF(J75&lt;=$U$22,$Z$22,IF(J75&lt;=$U$23,$Z$23,IF(J75&lt;=$U$24,$Z$24,IF(J75&lt;=$U$25,$Z$25,IF(J75&lt;=$U$26,$Z$26,IF(J75&lt;=$U$27,$Z$27,IF(J75&lt;=$U$28,$Z$28,IF(J75&lt;=$U$29,$Z$29,IF(J75&lt;=$U$30,$Z$30,0)))))))))))))</f>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
-  </mergeCells>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACD4CEE7-6601-5459-AC23-49332AD76DD5}">
-  <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="41.75" style="29" customWidth="1"/>
-    <col min="2" max="2" width="3" style="5" customWidth="1"/>
-    <col min="3" max="6" width="26.125" style="5" customWidth="1"/>
-    <col min="7" max="17" width="9" style="5"/>
-    <col min="18" max="18" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" style="5"/>
-    <col min="20" max="27" width="14.875" style="5" customWidth="1"/>
-    <col min="28" max="16384" width="9" style="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="E1" s="81" t="s">
-        <v>171</v>
-      </c>
-      <c r="F1" s="81">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A3" s="82" t="s">
-        <v>86</v>
-      </c>
-      <c r="B3" s="82"/>
-      <c r="C3" s="83" t="s">
-        <v>80</v>
-      </c>
-      <c r="D3" s="84" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="84" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="84"/>
-    </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A4" s="85" t="s">
-        <v>166</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'SIM_AIの金額'!D24</f>
-      </c>
-      <c r="D4" s="28">
-        <f>+'SIM_AIの金額'!G51</f>
-      </c>
-      <c r="E4" s="28">
-        <f>+'SIM_AIの金額'!J51</f>
-      </c>
-      <c r="F4" s="28"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A5" s="85" t="s">
-        <v>167</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'SIM_AIの金額'!D25</f>
-      </c>
-      <c r="D5" s="28">
-        <f>+'SIM_AIの金額'!G61</f>
-      </c>
-      <c r="E5" s="28">
-        <f>+'SIM_AIの金額'!J61</f>
-      </c>
-      <c r="F5" s="27"/>
-    </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A6" s="85" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="117">
-        <f>+'SIM_AIの金額'!D28</f>
-      </c>
-      <c r="D6" s="87">
-        <f>+'SIM_AIの金額'!G28</f>
-      </c>
-      <c r="E6" s="87">
-        <f>+'SIM_AIの金額'!J28</f>
-      </c>
-      <c r="F6" s="10"/>
-    </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A7" s="85" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="88">
-        <f>+'SIM_AIの金額'!D27</f>
-      </c>
-      <c r="D7" s="89">
-        <f>+'SIM_AIの金額'!G27</f>
-      </c>
-      <c r="E7" s="89">
-        <f>+'SIM_AIの金額'!J27</f>
-      </c>
-      <c r="F7" s="89"/>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A8" s="85" t="s">
-        <v>85</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="117">
-        <f>+'SIM_AIの金額'!D29</f>
-      </c>
-      <c r="D8" s="10">
-        <f>+'SIM_AIの金額'!G29</f>
-      </c>
-      <c r="E8" s="10">
-        <f>+'SIM_AIの金額'!J29</f>
-      </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A9" s="85"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A10" s="85" t="s">
-        <v>89</v>
-      </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="117">
-        <f>+'SIM_AIの金額'!D34</f>
-      </c>
-      <c r="D10" s="10">
-        <f>+'SIM_AIの金額'!G34</f>
-      </c>
-      <c r="E10" s="10">
-        <f>+'SIM_AIの金額'!J34</f>
-      </c>
-      <c r="F10" s="10"/>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A11" s="85" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="117">
-        <f>+'SIM_AIの金額'!D35</f>
-      </c>
-      <c r="D11" s="10">
-        <f>+'SIM_AIの金額'!G35</f>
-      </c>
-      <c r="E11" s="10">
-        <f>+'SIM_AIの金額'!J35</f>
-      </c>
-      <c r="F11" s="10"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A12" s="85" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="28">
-        <f>+IFERROR(C5/C11,0)</f>
-      </c>
-      <c r="D12" s="28">
-        <f>+D4/D11</f>
-      </c>
-      <c r="E12" s="28">
-        <f t="shared" ref="E12" si="0">+E4/E11</f>
-      </c>
-      <c r="F12" s="28"/>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A13" s="85" t="s">
-        <v>175</v>
-      </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="28">
-        <f>+IFERROR(C6/C12,0)</f>
-      </c>
-      <c r="D13" s="28">
-        <f>+D5/D11</f>
-      </c>
-      <c r="E13" s="28">
-        <f t="shared" ref="E13" si="1">+E5/E11</f>
-      </c>
-      <c r="F13" s="28"/>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A14" s="85"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="R14" s="29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A15" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募（サイト・仮に）</t>
-        </is>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="87">
-        <f>+'SIM_AIの金額'!$H$10</f>
-      </c>
-      <c r="D15" s="87">
-        <f>+'SIM_AIの金額'!$H$10</f>
-      </c>
-      <c r="E15" s="87">
-        <f>+'SIM_AIの金額'!$H$10</f>
-      </c>
-      <c r="F15" s="87"/>
-      <c r="R15" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A16" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV数（+LINEOA施策）</t>
-        </is>
-      </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="87">
-        <f>SUM(C17:C20)</f>
-      </c>
-      <c r="D16" s="87">
-        <f>SUM(D17:D20)</f>
-      </c>
-      <c r="E16" s="87">
-        <f>SUM(E17:E20)</f>
-      </c>
-      <c r="F16" s="87"/>
-      <c r="R16" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="V16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y16" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①_応募</t>
-        </is>
-      </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="87">
-        <f>+'SIM_AIの金額'!D36</f>
-      </c>
-      <c r="D17" s="87">
-        <f>+'SIM_AIの金額'!G36</f>
-      </c>
-      <c r="E17" s="87">
-        <f>+'SIM_AIの金額'!J36</f>
-      </c>
-      <c r="F17" s="10"/>
-      <c r="R17" s="5">
-        <v>0</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="T17" s="34">
-        <v>200000</v>
-      </c>
-      <c r="V17" s="5">
-        <v>0</v>
-      </c>
-      <c r="W17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="X17" s="34">
-        <v>600000</v>
-      </c>
-      <c r="Y17" s="35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A18" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="87">
-        <f>+'SIM_AIの金額'!D37</f>
-      </c>
-      <c r="D18" s="87">
-        <f>+'SIM_AIの金額'!G37</f>
-      </c>
-      <c r="E18" s="87">
-        <f>+'SIM_AIの金額'!J37</f>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="R18" s="34">
-        <v>200000</v>
-      </c>
-      <c r="S18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="T18" s="34">
-        <v>15000000</v>
-      </c>
-      <c r="V18" s="34">
-        <v>600000</v>
-      </c>
-      <c r="W18" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="X18" s="34">
-        <f>+T18*2.5</f>
-      </c>
-      <c r="Y18" s="35">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A19" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="87">
-        <f>+'SIM_AIの金額'!D38</f>
-      </c>
-      <c r="D19" s="87">
-        <f>+'SIM_AIの金額'!G38</f>
-      </c>
-      <c r="E19" s="87">
-        <f>+'SIM_AIの金額'!J38</f>
-      </c>
-      <c r="F19" s="10"/>
-      <c r="R19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="X19" s="34"/>
-      <c r="Y19" s="35"/>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A20" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="87">
-        <f>+'SIM_AIの金額'!D39</f>
-      </c>
-      <c r="D20" s="87">
-        <f>+'SIM_AIの金額'!G39</f>
-      </c>
-      <c r="E20" s="87">
-        <f>+'SIM_AIの金額'!J39</f>
-      </c>
-      <c r="F20" s="10"/>
-      <c r="R20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="X20" s="34"/>
-      <c r="Y20" s="35"/>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A21" s="85"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="R21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="X21" s="34"/>
-      <c r="Y21" s="35"/>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A22" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="90">
-        <f>+IFERROR(C4/C16,"--")</f>
-      </c>
-      <c r="D22" s="90">
-        <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
-      </c>
-      <c r="E22" s="90">
-        <f t="shared" si="2"/>
-      </c>
-      <c r="F22" s="90"/>
-      <c r="R22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="35"/>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A23" s="85" t="s">
-        <v>169</v>
-      </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="90">
-        <f>+IFERROR(C5/C16,"--")</f>
-      </c>
-      <c r="D23" s="90">
-        <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
-      </c>
-      <c r="E23" s="90">
-        <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
-      </c>
-      <c r="F23" s="90"/>
-      <c r="R23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="X23" s="34"/>
-      <c r="Y23" s="35"/>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A24" s="85"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="R24" s="34"/>
-      <c r="T24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="X24" s="34"/>
-      <c r="Y24" s="35"/>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A25" s="85" t="s">
-        <v>176</v>
-      </c>
-      <c r="B25" s="7"/>
-      <c r="C25" s="10">
-        <f>+'SIM_AIの金額'!E68+C29*C30</f>
-      </c>
-      <c r="D25" s="10">
-        <f>+'SIM_AIの金額'!G68+D29*D30</f>
-      </c>
-      <c r="E25" s="10">
-        <f>+'SIM_AIの金額'!J68+E29*E30</f>
-      </c>
-      <c r="F25" s="10"/>
-      <c r="R25" s="34"/>
-      <c r="T25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="35"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="R26" s="34"/>
-      <c r="T26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="X26" s="34"/>
-      <c r="Y26" s="35"/>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="R27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="35"/>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="R28" s="34"/>
-      <c r="T28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="35"/>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A29" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="C29" s="5">
-        <f>+IF(C10&lt;=30000,0,C10-30000)</f>
-      </c>
-      <c r="D29" s="91">
-        <f>+IF(D10&lt;=30000,0,D10-30000)</f>
-      </c>
-      <c r="E29" s="91">
-        <f>+IF(E10&lt;=30000,0,E10-30000)</f>
-      </c>
-      <c r="F29" s="91"/>
-      <c r="R29" s="34"/>
-      <c r="T29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="X29" s="34"/>
-      <c r="Y29" s="35"/>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A30" s="29" t="s">
-        <v>170</v>
-      </c>
-      <c r="C30" s="5">
-        <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-      </c>
-      <c r="D30" s="5">
-        <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-      </c>
-      <c r="E30" s="5">
-        <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
-      </c>
-      <c r="R30" s="34"/>
-      <c r="T30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="X30" s="34"/>
-      <c r="Y30" s="35"/>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="R31" s="34"/>
-      <c r="T31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="Y31" s="35"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A35" s="92" t="s">
-        <v>125</v>
-      </c>
-      <c r="B35" s="92"/>
-      <c r="C35" s="93" t="s">
-        <v>163</v>
-      </c>
-      <c r="D35" s="94" t="s">
-        <v>164</v>
-      </c>
-      <c r="E35" s="94" t="s">
-        <v>165</v>
-      </c>
-      <c r="F35" s="94" t="s">
-        <v>165</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -4111,28 +4111,28 @@
         <v>0</v>
       </c>
       <c r="E27" s="47">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="F27" s="47">
-        <v>0.384</v>
+        <f>+E27*1.025</f>
       </c>
       <c r="G27" s="47">
-        <v>0.388</v>
+        <f>+F27*1.025</f>
       </c>
       <c r="H27" s="47">
-        <v>0.392</v>
+        <f>+G27*1.025</f>
       </c>
       <c r="I27" s="47">
-        <v>0.396</v>
+        <f>+H27*1.025</f>
       </c>
       <c r="J27" s="47">
-        <v>0.4</v>
+        <f>+I27*1.025</f>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブロック率：求人は用が済むとブロックされやすいので、38%から少しずつ上がる想定</t>
+          <t xml:space="preserve">ブロック率：1か月目34%（殿村さん）。2か月目以降は前の月×1.025（FMTの式）</t>
         </is>
       </c>
       <c r="O27" s="17" t="s">

--- a/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -13,7 +13,7 @@
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="SIM_竹（コンサル基本）" sheetId="1" r:id="rId1"/>
+    <sheet name="SIM_コンサル基本" sheetId="1" r:id="rId1"/>
     <sheet name="SIM_比較" sheetId="2" r:id="rId2"/>
     <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -4263,7 +4263,7 @@
       <c r="L30" s="7"/>
       <c r="N30" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">企画配信 月3回（業界資料の竹＝コンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
+          <t xml:space="preserve">企画配信 月3回（業界資料のコンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
         </is>
       </c>
       <c r="O30" s="17" t="s">
@@ -5364,7 +5364,7 @@
       <c r="A69" s="15"/>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）</t>
+          <t xml:space="preserve">LINE運用コンサル（コンサル基本）</t>
         </is>
       </c>
       <c r="C69" s="90">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="N69" s="69" t="inlineStr">
         <is>
-          <t xml:space="preserve">LINE運用コンサル（竹：コンサル基本）月20万円。初期は初期30万円</t>
+          <t xml:space="preserve">LINE運用コンサル（コンサル基本）月20万円。初期は初期30万円</t>
         </is>
       </c>
       <c r="O69" s="5" t="s">
@@ -5678,13 +5678,13 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="86">
-        <f>+'SIM_竹（コンサル基本）'!D24</f>
+        <f>+'SIM_コンサル基本'!D24</f>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM_竹（コンサル基本）'!G51</f>
+        <f>+'SIM_コンサル基本'!G51</f>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM_竹（コンサル基本）'!J51</f>
+        <f>+'SIM_コンサル基本'!J51</f>
       </c>
       <c r="F4" s="28"/>
     </row>
@@ -5694,13 +5694,13 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="86">
-        <f>+'SIM_竹（コンサル基本）'!D25</f>
+        <f>+'SIM_コンサル基本'!D25</f>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM_竹（コンサル基本）'!G61</f>
+        <f>+'SIM_コンサル基本'!G61</f>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM_竹（コンサル基本）'!J61</f>
+        <f>+'SIM_コンサル基本'!J61</f>
       </c>
       <c r="F5" s="27"/>
     </row>
@@ -5710,13 +5710,13 @@
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM_竹（コンサル基本）'!D28</f>
+        <f>+'SIM_コンサル基本'!D28</f>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM_竹（コンサル基本）'!G28</f>
+        <f>+'SIM_コンサル基本'!G28</f>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM_竹（コンサル基本）'!J28</f>
+        <f>+'SIM_コンサル基本'!J28</f>
       </c>
       <c r="F6" s="10"/>
     </row>
@@ -5726,13 +5726,13 @@
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM_竹（コンサル基本）'!D27</f>
+        <f>+'SIM_コンサル基本'!D27</f>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM_竹（コンサル基本）'!G27</f>
+        <f>+'SIM_コンサル基本'!G27</f>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM_竹（コンサル基本）'!J27</f>
+        <f>+'SIM_コンサル基本'!J27</f>
       </c>
       <c r="F7" s="89"/>
     </row>
@@ -5742,13 +5742,13 @@
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM_竹（コンサル基本）'!D29</f>
+        <f>+'SIM_コンサル基本'!D29</f>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM_竹（コンサル基本）'!G29</f>
+        <f>+'SIM_コンサル基本'!G29</f>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM_竹（コンサル基本）'!J29</f>
+        <f>+'SIM_コンサル基本'!J29</f>
       </c>
       <c r="F8" s="10"/>
     </row>
@@ -5766,13 +5766,13 @@
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM_竹（コンサル基本）'!D34</f>
+        <f>+'SIM_コンサル基本'!D34</f>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM_竹（コンサル基本）'!G34</f>
+        <f>+'SIM_コンサル基本'!G34</f>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM_竹（コンサル基本）'!J34</f>
+        <f>+'SIM_コンサル基本'!J34</f>
       </c>
       <c r="F10" s="10"/>
     </row>
@@ -5782,13 +5782,13 @@
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM_竹（コンサル基本）'!D35</f>
+        <f>+'SIM_コンサル基本'!D35</f>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM_竹（コンサル基本）'!G35</f>
+        <f>+'SIM_コンサル基本'!G35</f>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM_竹（コンサル基本）'!J35</f>
+        <f>+'SIM_コンサル基本'!J35</f>
       </c>
       <c r="F11" s="10"/>
     </row>
@@ -5843,13 +5843,13 @@
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <f>+'SIM_コンサル基本'!$H$10</f>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <f>+'SIM_コンサル基本'!$H$10</f>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <f>+'SIM_コンサル基本'!$H$10</f>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
@@ -5891,13 +5891,13 @@
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM_竹（コンサル基本）'!D36</f>
+        <f>+'SIM_コンサル基本'!D36</f>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM_竹（コンサル基本）'!G36</f>
+        <f>+'SIM_コンサル基本'!G36</f>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM_竹（コンサル基本）'!J36</f>
+        <f>+'SIM_コンサル基本'!J36</f>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
@@ -5930,13 +5930,13 @@
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM_竹（コンサル基本）'!D37</f>
+        <f>+'SIM_コンサル基本'!D37</f>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM_竹（コンサル基本）'!G37</f>
+        <f>+'SIM_コンサル基本'!G37</f>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM_竹（コンサル基本）'!J37</f>
+        <f>+'SIM_コンサル基本'!J37</f>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
@@ -5969,13 +5969,13 @@
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM_竹（コンサル基本）'!D38</f>
+        <f>+'SIM_コンサル基本'!D38</f>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM_竹（コンサル基本）'!G38</f>
+        <f>+'SIM_コンサル基本'!G38</f>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM_竹（コンサル基本）'!J38</f>
+        <f>+'SIM_コンサル基本'!J38</f>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5992,13 +5992,13 @@
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM_竹（コンサル基本）'!D39</f>
+        <f>+'SIM_コンサル基本'!D39</f>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM_竹（コンサル基本）'!G39</f>
+        <f>+'SIM_コンサル基本'!G39</f>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM_竹（コンサル基本）'!J39</f>
+        <f>+'SIM_コンサル基本'!J39</f>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -6081,13 +6081,13 @@
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM_竹（コンサル基本）'!E68+C29*C30</f>
+        <f>+'SIM_コンサル基本'!E68+C29*C30</f>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM_竹（コンサル基本）'!G68+D29*D30</f>
+        <f>+'SIM_コンサル基本'!G68+D29*D30</f>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM_竹（コンサル基本）'!J68+E29*E30</f>
+        <f>+'SIM_コンサル基本'!J68+E29*E30</f>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>

--- a/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
+++ b/清水グループ御中_LINEOA施策提案【SIM】ver1.0.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samura-n\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tonomura-r\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29A23919-D8B6-4451-9491-3DC3CF42E353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6D6185A-6648-444F-985E-BB6324877977}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
+    <workbookView xWindow="-13380" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{02433765-3560-48F5-BC99-B30FC64129A4}"/>
   </bookViews>
   <sheets>
-    <sheet name="SIM_コンサル基本" sheetId="1" r:id="rId1"/>
+    <sheet name="SIM_竹（コンサル基本）" sheetId="1" r:id="rId1"/>
     <sheet name="SIM_比較" sheetId="2" r:id="rId2"/>
     <sheet name="SIM考え方" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr fullCalcOnLoad="1" calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="192">
   <si>
     <t>項目</t>
     <rPh sb="0" eb="2">
@@ -78,23 +78,6 @@
   </si>
   <si>
     <t>CPF</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>離脱防止</t>
-    <rPh sb="0" eb="2">
-      <t>リダツ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ボウシ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>サンクス誘導</t>
-    <rPh sb="4" eb="6">
-      <t>ユウドウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -552,10 +535,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>UU</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>CVR</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -578,48 +557,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>1か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>2か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>3か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>4か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>5か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>6か月目</t>
-    <rPh sb="2" eb="4">
-      <t>ゲツメ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>想定顧客リスト</t>
     <rPh sb="0" eb="2">
       <t>ソウテイ</t>
@@ -713,23 +650,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>CV数（もともと）</t>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CV数（+LINEOA施策）</t>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シサク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>メッセ通数</t>
     <rPh sb="3" eb="5">
       <t>ツウスウ</t>
@@ -744,52 +664,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>OA施策CV_内訳①_新規CV1</t>
-    <rPh sb="2" eb="4">
-      <t>シサク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ウチワケ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シンキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>OA施策CV_内訳②_新規CV2</t>
-    <rPh sb="2" eb="4">
-      <t>シサク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ウチワケ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>シンキ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>OA施策CV_内訳④_リピCV4</t>
-    <rPh sb="2" eb="4">
-      <t>シサク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ウチワケ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>OA施策CV_内訳③_リピCV3</t>
-    <rPh sb="2" eb="4">
-      <t>シサク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ウチワケ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>友だち数_増加施策</t>
     <rPh sb="0" eb="1">
       <t>トモ</t>
@@ -1100,16 +974,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>SimilarWeb等を参考に</t>
-    <rPh sb="10" eb="11">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>サンコウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>広告比率等を参考に</t>
     <rPh sb="0" eb="5">
       <t>コウコクヒリツトウ</t>
@@ -1120,19 +984,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>CV聞けてれば→通知メッセ、サンクスLINE誘導</t>
-    <rPh sb="2" eb="3">
-      <t>キ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ツウチ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>ユウドウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>通知メッセージ_CV</t>
     <rPh sb="0" eb="2">
       <t>ツウチ</t>
@@ -1233,47 +1084,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>離脱防止表示率×UU×クリック率×実追加率</t>
-    <rPh sb="0" eb="4">
-      <t>リダツボウシ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="15" eb="16">
-      <t>リツ</t>
-    </rPh>
-    <rPh sb="17" eb="18">
-      <t>ジツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>リツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CV(別施策)*誘導成功率*実追加率</t>
-    <rPh sb="3" eb="6">
-      <t>ベツシサク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="10" eb="13">
-      <t>セイコウリツ</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>ジツツイカリツ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>サンクス到達*情報一致率(70%前後)*実追加率</t>
     <rPh sb="4" eb="6">
       <t>トウタツ</t>
@@ -1300,26 +1110,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>※上記記載に追加して、LP、HPからのLINE誘導を加味する</t>
-    <rPh sb="1" eb="5">
-      <t>ジョウキキサイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>カミ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>CV（別施策）1</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>CV（別施策）2</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1347,38 +1137,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>サンクス誘導：初期10万円/通期5万円　※20%のコストカットOK</t>
-    <rPh sb="4" eb="6">
-      <t>ユウドウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ショキ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>マンエン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ツウキ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>マンエン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>UUにかかわらず、10000円/月にて設定</t>
-    <rPh sb="14" eb="15">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="16" eb="17">
-      <t>ツキ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>セッテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>機能拡張</t>
     <rPh sb="0" eb="4">
       <t>キノウカクチョウ</t>
@@ -1396,16 +1154,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>コンサル費用固定</t>
-    <rPh sb="4" eb="6">
-      <t>ヒヨウ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コテイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コンサル費用ショット（開発、初期費用）</t>
     <rPh sb="4" eb="6">
       <t>ヒヨウ</t>
@@ -1426,61 +1174,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <r>
-      <t>アカウント費用（15000円or5000円）＋従量課金　</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="メイリオ"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※5000通を超える場合15000円～の設定にする ※重量課金は要確認</t>
-    </r>
-    <rPh sb="5" eb="7">
-      <t>ヒヨウ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="23" eb="27">
-      <t>ジュウリョウカキン</t>
-    </rPh>
-    <rPh sb="33" eb="34">
-      <t>ツウ</t>
-    </rPh>
-    <rPh sb="35" eb="36">
-      <t>コ</t>
-    </rPh>
-    <rPh sb="38" eb="40">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="45" eb="46">
-      <t>エン</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="55" eb="57">
-      <t>ジュウリョウ</t>
-    </rPh>
-    <rPh sb="57" eb="59">
-      <t>カキン</t>
-    </rPh>
-    <rPh sb="60" eb="61">
-      <t>ヨウ</t>
-    </rPh>
-    <rPh sb="61" eb="63">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>コスト想定(固定費)</t>
     <rPh sb="3" eb="5">
       <t>ソウテイ</t>
@@ -1491,41 +1184,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>←基本本数が4本として設計する</t>
-    <rPh sb="1" eb="5">
-      <t>キホンホンスウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>←基本本数が4本として設計する（ユーザー数と固定費で調整）</t>
-    <rPh sb="1" eb="5">
-      <t>キホンホンスウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>セッケイ</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="22" eb="25">
-      <t>コテイヒ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>チョウセイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>※ターゲット数の増加分が通常の増加分を超えないように調整する</t>
     <rPh sb="6" eb="7">
       <t>スウ</t>
@@ -1678,10 +1336,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>想定CPC（LINEOA施策）_成果報酬プラン</t>
     <rPh sb="0" eb="2">
       <t>ソウテイ</t>
@@ -1727,13 +1381,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>広告・アフィUU</t>
-    <rPh sb="0" eb="2">
-      <t>コウコク</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>現状数値</t>
     <rPh sb="0" eb="4">
       <t>ゲンジョウスウチ</t>
@@ -1768,18 +1415,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>購入（新規）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>購入（リピート）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>初期構築費</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>マネタイズ（イメージ）</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -1818,10 +1453,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>株式会社御中_LINEOA施策提案【SIM】</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>KaiU表示率</t>
     <rPh sb="4" eb="6">
       <t>ヒョウジ</t>
@@ -1845,6 +1476,96 @@
   <si>
     <t>Ver.</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>清水グループ御中_LINEOA施策提案【SIM】（離脱防止＋サイトのLINEボタン＋サンクスLINE誘導）</t>
+  </si>
+  <si>
+    <t>応募</t>
+  </si>
+  <si>
+    <t>サイトUU</t>
+  </si>
+  <si>
+    <t>CV①応募：LINEのリンクからの応募だけ。サンクスLINEで友だちになった方（応募済み）の応募は数えない</t>
+  </si>
+  <si>
+    <t>うち広告</t>
+  </si>
+  <si>
+    <t>応募（サイト・仮に）</t>
+  </si>
+  <si>
+    <t>サイトからの応募は与件に無いので、仮にUUの1.5%（月134件）</t>
+  </si>
+  <si>
+    <t>1か月目</t>
+  </si>
+  <si>
+    <t>2か月目</t>
+  </si>
+  <si>
+    <t>3か月目</t>
+  </si>
+  <si>
+    <t>4か月目</t>
+  </si>
+  <si>
+    <t>5か月目</t>
+  </si>
+  <si>
+    <t>6か月目</t>
+  </si>
+  <si>
+    <t>求人サイトの月間UU 8,947（与件）。6か月同じ</t>
+  </si>
+  <si>
+    <t>離脱防止ポップアップ</t>
+  </si>
+  <si>
+    <t>離脱防止ポップアップ＝UU×表示65%×クリック12.5%×追加12.5%（定義テキストの係数）</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導＝応募×遷移80%×追加45%（定義テキストの係数）</t>
+  </si>
+  <si>
+    <t>サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止＋サンクスLINE誘導</t>
+  </si>
+  <si>
+    <t>ブロック率：求人は用が済むとブロックされやすいので、38%から少しずつ上がる想定</t>
+  </si>
+  <si>
+    <t>企画配信 月3回（業界資料の竹＝コンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
+  </si>
+  <si>
+    <t>ステップ配信3通（友だち追加の翌日以降。職種ごとに中身を分ける）</t>
+  </si>
+  <si>
+    <t>応募：クリックの0.3〜1.0%前後</t>
+  </si>
+  <si>
+    <t>離脱防止ポップアップ：初期1.5万円・月3万円</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導</t>
+  </si>
+  <si>
+    <t>サンクスLINE誘導：初期15万円・月3万円〜</t>
+  </si>
+  <si>
+    <t>アカウント費：FMTの式（開設3万円）</t>
+  </si>
+  <si>
+    <t>LINE運用コンサル（竹：コンサル基本）</t>
+  </si>
+  <si>
+    <t>LINE運用コンサル（竹：コンサル基本）月20万円。初期は初期30万円</t>
+  </si>
+  <si>
+    <t>CV数（+LINEOA施策）</t>
+  </si>
+  <si>
+    <t>CV①_応募</t>
   </si>
 </sst>
 </file>
@@ -1855,7 +1576,7 @@
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2038,13 +1759,6 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.249977111117893"/>
-      <name val="メイリオ"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="メイリオ"/>
       <family val="3"/>
       <charset val="128"/>
@@ -2352,7 +2066,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="157">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2722,72 +2436,6 @@
     <xf numFmtId="38" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2810,9 +2458,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="8" fillId="7" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2846,6 +2491,72 @@
     </xf>
     <xf numFmtId="14" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -3202,38 +2913,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7C635F9-36D4-435E-B89B-2E9FE9727E52}">
   <dimension ref="A2:Z76"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
     <col min="2" max="2" width="29.25" style="5" customWidth="1"/>
     <col min="3" max="12" width="20" style="5" customWidth="1"/>
-    <col min="13" max="13" width="2.625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="2.58203125" style="5" customWidth="1"/>
     <col min="14" max="14" width="44.5" style="69" customWidth="1"/>
-    <col min="15" max="17" width="24.125" style="5" customWidth="1"/>
-    <col min="18" max="18" width="2.875" style="5" customWidth="1"/>
-    <col min="19" max="19" width="12.125" style="5" customWidth="1"/>
-    <col min="20" max="20" width="2.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.125" style="5" customWidth="1"/>
-    <col min="22" max="22" width="2.875" style="5" customWidth="1"/>
-    <col min="23" max="23" width="12.125" style="5" customWidth="1"/>
-    <col min="24" max="24" width="2.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="12.125" style="5" customWidth="1"/>
+    <col min="15" max="17" width="24.08203125" style="5" customWidth="1"/>
+    <col min="18" max="18" width="2.83203125" style="5" customWidth="1"/>
+    <col min="19" max="19" width="12.08203125" style="5" customWidth="1"/>
+    <col min="20" max="20" width="2.58203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.08203125" style="5" customWidth="1"/>
+    <col min="22" max="22" width="2.83203125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="12.08203125" style="5" customWidth="1"/>
+    <col min="24" max="24" width="2.58203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="12.08203125" style="5" customWidth="1"/>
     <col min="26" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A2" s="156" t="s">
-        <v>194</v>
-      </c>
-      <c r="B2" s="157">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="133" t="s">
+        <v>161</v>
+      </c>
+      <c r="B2" s="134">
         <v>46314</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">清水グループ御中_LINEOA施策提案【SIM】（離脱防止＋サイトのLINEボタン＋サンクスLINE誘導）</t>
-        </is>
+    <row r="4" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="56" t="s">
+        <v>162</v>
       </c>
       <c r="N4" s="55"/>
       <c r="O4" s="55"/>
@@ -3248,13 +2957,13 @@
       <c r="X4" s="55"/>
       <c r="Y4" s="55"/>
     </row>
-    <row r="5" spans="1:25" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" s="2" customFormat="1" ht="22.5" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="N5" s="55" t="s">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="O5" s="55"/>
       <c r="P5" s="55"/>
@@ -3268,7 +2977,7 @@
       <c r="X5" s="55"/>
       <c r="Y5" s="55"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="N6" s="55"/>
       <c r="O6" s="55"/>
       <c r="P6" s="55"/>
@@ -3282,155 +2991,137 @@
       <c r="X6" s="55"/>
       <c r="Y6" s="55"/>
     </row>
-    <row r="7" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A7" s="29" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="130" t="s">
+    </row>
+    <row r="8" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="137" t="s">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="33">
+        <v>0</v>
+      </c>
+      <c r="G8" s="121" t="s">
+        <v>164</v>
+      </c>
+      <c r="H8" s="122">
+        <v>8947</v>
+      </c>
+      <c r="I8" s="123"/>
+      <c r="J8" s="123" t="s">
+        <v>69</v>
+      </c>
+      <c r="K8" s="129">
+        <v>0</v>
+      </c>
+      <c r="N8" s="69" t="s">
+        <v>165</v>
+      </c>
+      <c r="O8" s="35" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="138"/>
+      <c r="B9" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C9" s="38" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="33">
+        <v>0</v>
+      </c>
+      <c r="G9" s="124" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="125">
+        <v>0</v>
+      </c>
+      <c r="I9" s="22"/>
+      <c r="J9" s="29"/>
+      <c r="K9" s="118"/>
+      <c r="N9" s="132" t="s">
+        <v>111</v>
+      </c>
+      <c r="O9" s="130" t="s">
+        <v>155</v>
+      </c>
+      <c r="P9" s="131" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" s="137" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募</t>
-        </is>
-      </c>
-      <c r="D8" s="33">
-        <v>0</v>
-      </c>
-      <c r="G8" s="143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトUU</t>
-        </is>
-      </c>
-      <c r="H8" s="144">
-        <v>8947</v>
-      </c>
-      <c r="I8" s="145"/>
-      <c r="J8" s="145" t="s">
-        <v>78</v>
-      </c>
-      <c r="K8" s="152">
-        <v>0</v>
-      </c>
-      <c r="N8" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①応募：LINEのリンクからの応募だけ。サンクスLINEで友だちになった方（応募済み）の応募は数えない</t>
-        </is>
-      </c>
-      <c r="O8" s="35" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="9" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="131"/>
-      <c r="B9" s="19" t="s">
+      <c r="B10" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D9" s="33">
-        <v>0</v>
-      </c>
-      <c r="G9" s="146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">うち広告</t>
-        </is>
-      </c>
-      <c r="H9" s="147">
-        <v>0</v>
-      </c>
-      <c r="I9" s="148"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="140"/>
-      <c r="N9" s="155" t="s">
-        <v>127</v>
-      </c>
-      <c r="O9" s="153" t="s">
-        <v>187</v>
-      </c>
-      <c r="P9" s="154" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A10" s="130" t="s">
+      <c r="C10" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="33">
+        <v>0</v>
+      </c>
+      <c r="G10" s="124" t="s">
+        <v>167</v>
+      </c>
+      <c r="H10" s="125">
+        <v>134</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="J10" s="29"/>
+      <c r="K10" s="118"/>
+      <c r="N10" s="132" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" ht="18" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="138"/>
+      <c r="B11" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
-      </c>
-      <c r="D10" s="33">
-        <v>0</v>
-      </c>
-      <c r="G10" s="146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募（サイト・仮に）</t>
-        </is>
-      </c>
-      <c r="H10" s="147">
-        <v>134</v>
-      </c>
-      <c r="I10" s="148" t="s">
-        <v>186</v>
-      </c>
-      <c r="J10" s="139"/>
-      <c r="K10" s="140"/>
-      <c r="N10" s="155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトからの応募は与件に無いので、仮にUUの1.5%（月134件）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:25" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="131"/>
-      <c r="B11" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="38" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+      <c r="C11" s="38" t="s">
+        <v>61</v>
       </c>
       <c r="D11" s="33">
         <v>0</v>
       </c>
-      <c r="G11" s="149" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="150">
-        <v>0</v>
-      </c>
-      <c r="I11" s="151" t="s">
-        <v>185</v>
-      </c>
-      <c r="J11" s="141"/>
-      <c r="K11" s="142"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+      <c r="G11" s="126" t="s">
+        <v>124</v>
+      </c>
+      <c r="H11" s="127">
+        <v>0</v>
+      </c>
+      <c r="I11" s="128" t="s">
+        <v>153</v>
+      </c>
+      <c r="J11" s="119"/>
+      <c r="K11" s="120"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="O12" s="55" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="P12" s="55"/>
       <c r="Q12" s="55"/>
@@ -3439,44 +3130,32 @@
       <c r="U12" s="55"/>
       <c r="V12" s="55"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A13" s="132" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" s="132"/>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="139" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="139"/>
       <c r="C13" s="95"/>
       <c r="D13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1か月目</t>
-        </is>
-      </c>
-      <c r="F13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2か月目</t>
-        </is>
-      </c>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3か月目</t>
-        </is>
-      </c>
-      <c r="H13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4か月目</t>
-        </is>
-      </c>
-      <c r="I13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5か月目</t>
-        </is>
-      </c>
-      <c r="J13" s="36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6か月目</t>
-        </is>
+        <v>28</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>169</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="G13" s="36" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>172</v>
+      </c>
+      <c r="I13" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="J13" s="36" t="s">
+        <v>174</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>1</v>
@@ -3485,10 +3164,10 @@
         <v>2</v>
       </c>
       <c r="N13" s="71" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="O13" s="30" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="P13" s="23"/>
       <c r="Q13" s="23"/>
@@ -3497,129 +3176,148 @@
       <c r="U13" s="23"/>
       <c r="V13" s="23"/>
     </row>
-    <row r="14" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A14" s="133" t="s">
-        <v>33</v>
+    <row r="14" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="140" t="s">
+        <v>31</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" s="99"/>
       <c r="D14" s="42">
         <f>+H8</f>
+        <v>8947</v>
       </c>
       <c r="E14" s="43">
         <f>+D14</f>
+        <v>8947</v>
       </c>
       <c r="F14" s="43">
         <f t="shared" ref="F14:J14" si="0">+E14</f>
+        <v>8947</v>
       </c>
       <c r="G14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="H14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="I14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="J14" s="43">
         <f t="shared" si="0"/>
+        <v>8947</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="7"/>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">求人サイトの月間UU 8,947（与件）。6か月同じ</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="134"/>
+      <c r="N14" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="141"/>
       <c r="B15" s="20" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="99"/>
       <c r="D15" s="42">
         <f t="shared" ref="D15" si="1">+H9</f>
+        <v>0</v>
       </c>
       <c r="E15" s="43">
         <f t="shared" ref="E15:J16" si="2">+D15</f>
+        <v>0</v>
       </c>
       <c r="F15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="H15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="I15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="J15" s="43">
         <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="K15" s="11"/>
       <c r="L15" s="7"/>
       <c r="N15" s="69" t="s">
-        <v>193</v>
+        <v>160</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="P15" s="79">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A16" s="135"/>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="142"/>
       <c r="B16" s="20" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="C16" s="99"/>
       <c r="D16" s="42">
         <f>H10</f>
+        <v>134</v>
       </c>
       <c r="E16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="F16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="G16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="H16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="I16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="J16" s="43">
         <f t="shared" si="2"/>
+        <v>134</v>
       </c>
       <c r="K16" s="11"/>
       <c r="L16" s="7"/>
       <c r="N16" s="69" t="s">
-        <v>192</v>
+        <v>159</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="P16" s="79">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="S16" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A17" s="133" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="140" t="s">
         <v>3</v>
       </c>
       <c r="B17" s="8" t="s">
@@ -3648,27 +3346,25 @@
         <v>0</v>
       </c>
       <c r="K17" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L17" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="S17" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="W17" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z17" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="W17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z17" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A18" s="134"/>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="141"/>
+      <c r="B18" s="8" t="s">
+        <v>176</v>
       </c>
       <c r="C18" s="100"/>
       <c r="D18" s="58" t="b">
@@ -3693,16 +3389,16 @@
         <v>1</v>
       </c>
       <c r="K18" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L18" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="N18" s="69" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="O18" s="22" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="P18" s="78">
         <v>0.65</v>
@@ -3711,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="T18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="U18" s="34">
         <v>200000</v>
@@ -3720,7 +3416,7 @@
         <v>0</v>
       </c>
       <c r="X18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y18" s="34">
         <v>600000</v>
@@ -3729,10 +3425,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A19" s="134"/>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="141"/>
       <c r="B19" s="8" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C19" s="100"/>
       <c r="D19" s="58" t="b">
@@ -3759,10 +3455,10 @@
       <c r="K19" s="14"/>
       <c r="L19" s="9"/>
       <c r="N19" s="69" t="s">
-        <v>191</v>
+        <v>158</v>
       </c>
       <c r="O19" s="22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P19" s="78">
         <v>0.55000000000000004</v>
@@ -3771,7 +3467,7 @@
         <v>200000</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="U19" s="34">
         <v>15000000</v>
@@ -3780,19 +3476,20 @@
         <v>600000</v>
       </c>
       <c r="X19" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y19" s="34">
         <f>+U19*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Z19" s="35">
         <v>2.5</v>
       </c>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A20" s="134"/>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="141"/>
       <c r="B20" s="8" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="C20" s="100"/>
       <c r="D20" s="58" t="b">
@@ -3824,10 +3521,10 @@
       <c r="Y20" s="34"/>
       <c r="Z20" s="35"/>
     </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.4">
-      <c r="A21" s="135"/>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="142"/>
       <c r="B21" s="8" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="C21" s="100"/>
       <c r="D21" s="58" t="b">
@@ -3852,13 +3549,13 @@
         <v>0</v>
       </c>
       <c r="K21" s="14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="O21" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="P21" s="26"/>
       <c r="S21" s="34"/>
@@ -3867,16 +3564,16 @@
       <c r="Y21" s="34"/>
       <c r="Z21" s="35"/>
     </row>
-    <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="136" t="s">
-        <v>13</v>
+    <row r="22" spans="1:26" ht="18.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="143" t="s">
+        <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>4</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E22" s="63">
         <v>0</v>
@@ -3899,10 +3596,10 @@
       <c r="K22" s="11"/>
       <c r="L22" s="7"/>
       <c r="N22" s="69" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="O22" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P22" s="24">
         <v>0.78</v>
@@ -3913,50 +3610,52 @@
       <c r="Y22" s="34"/>
       <c r="Z22" s="35"/>
     </row>
-    <row r="23" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A23" s="134"/>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="141"/>
+      <c r="B23" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E23" s="46">
-        <f>IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
+        <f t="shared" ref="E23:J23" si="3">IF(E18=FALSE,0,E14*$P$18*0.125*0.125)</f>
+        <v>90.867968750000003</v>
       </c>
       <c r="F23" s="46">
-        <f>IF(F18=FALSE,0,F14*$P$18*0.125*0.125)</f>
+        <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="G23" s="63">
-        <f>IF(G18=FALSE,0,G14*$P$18*0.125*0.125)</f>
+        <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="H23" s="63">
-        <f>IF(H18=FALSE,0,H14*$P$18*0.125*0.125)</f>
+        <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="I23" s="63">
-        <f>IF(I18=FALSE,0,I14*$P$18*0.125*0.125)</f>
+        <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="J23" s="63">
-        <f>IF(J18=FALSE,0,J14*$P$18*0.125*0.125)</f>
+        <f t="shared" si="3"/>
+        <v>90.867968750000003</v>
       </c>
       <c r="K23" s="11"/>
       <c r="L23" s="7"/>
-      <c r="N23" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ＝UU×表示65%×クリック12.5%×追加12.5%（定義テキストの係数）</t>
-        </is>
+      <c r="N23" s="69" t="s">
+        <v>177</v>
       </c>
       <c r="O23" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P23" s="24">
         <v>0.1</v>
       </c>
       <c r="Q23" s="5" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="S23" s="34"/>
       <c r="U23" s="34"/>
@@ -3964,42 +3663,46 @@
       <c r="Y23" s="34"/>
       <c r="Z23" s="35"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A24" s="134"/>
+    <row r="24" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="141"/>
       <c r="B24" s="6" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E24" s="46">
-        <f>IF(E19=FALSE,0,E16*0.8*0.45)</f>
+        <f t="shared" ref="E24:J24" si="4">IF(E19=FALSE,0,E16*0.8*0.45)</f>
+        <v>48.24</v>
       </c>
       <c r="F24" s="63">
-        <f>IF(F19=FALSE,0,F16*0.8*0.45)</f>
+        <f t="shared" si="4"/>
+        <v>48.24</v>
       </c>
       <c r="G24" s="63">
-        <f>IF(G19=FALSE,0,G16*0.8*0.45)</f>
+        <f t="shared" si="4"/>
+        <v>48.24</v>
       </c>
       <c r="H24" s="63">
-        <f>IF(H19=FALSE,0,H16*0.8*0.45)</f>
+        <f t="shared" si="4"/>
+        <v>48.24</v>
       </c>
       <c r="I24" s="63">
-        <f>IF(I19=FALSE,0,I16*0.8*0.45)</f>
+        <f t="shared" si="4"/>
+        <v>48.24</v>
       </c>
       <c r="J24" s="63">
-        <f>IF(J19=FALSE,0,J16*0.8*0.45)</f>
+        <f t="shared" si="4"/>
+        <v>48.24</v>
       </c>
       <c r="K24" s="11"/>
       <c r="L24" s="7"/>
-      <c r="N24" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導＝応募×遷移80%×追加45%（定義テキストの係数）</t>
-        </is>
+      <c r="N24" s="69" t="s">
+        <v>178</v>
       </c>
       <c r="O24" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P24" s="77">
         <v>0.8</v>
@@ -4013,40 +3716,46 @@
       <c r="Y24" s="34"/>
       <c r="Z24" s="35"/>
     </row>
-    <row r="25" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A25" s="135"/>
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="142"/>
       <c r="B25" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C25" s="17"/>
       <c r="D25" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E25" s="46">
         <f>+IF(E20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="F25" s="46">
         <f t="shared" ref="F25:J25" si="5">+IF(F20=FALSE,0,SUM($H$10:$H$11)*0.7*0.3)+IF($E$21=FALSE,0,$K$8*0.15*0.15)</f>
+        <v>0</v>
       </c>
       <c r="G25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="H25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="I25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="J25" s="46">
         <f t="shared" si="5"/>
+        <v>0</v>
       </c>
       <c r="K25" s="11"/>
       <c r="L25" s="7"/>
       <c r="N25" s="69" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="O25" s="25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="P25" s="26"/>
       <c r="S25" s="34"/>
@@ -4055,42 +3764,46 @@
       <c r="Y25" s="34"/>
       <c r="Z25" s="35"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A26" s="120" t="s">
-        <v>17</v>
-      </c>
-      <c r="B26" s="121"/>
+    <row r="26" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="145"/>
       <c r="C26" s="23"/>
       <c r="D26" s="44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E26" s="46">
         <f>+SUM(E22:E25)+$H$9*$P$16+($H$8-$H$9)*$P$15+IF(P9=FALSE,0,$K$8*0.15*0.08)</f>
+        <v>183.84296875000001</v>
       </c>
       <c r="F26" s="46">
         <f t="shared" ref="F26:J26" si="6">+SUM(F22:F25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>183.84296875000001</v>
       </c>
       <c r="G26" s="46">
         <f>+SUM(G22:G25)+$H$9*$P$16+($H$8-$H$9)*$P$15</f>
+        <v>183.84296875000001</v>
       </c>
       <c r="H26" s="46">
         <f t="shared" si="6"/>
+        <v>183.84296875000001</v>
       </c>
       <c r="I26" s="46">
         <f t="shared" si="6"/>
+        <v>183.84296875000001</v>
       </c>
       <c r="J26" s="46">
         <f t="shared" si="6"/>
+        <v>183.84296875000001</v>
       </c>
       <c r="K26" s="11"/>
       <c r="L26" s="7"/>
-      <c r="N26" s="72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サイトのLINEボタン（UUの0.5%・FMTの係数）＋離脱防止＋サンクスLINE誘導</t>
-        </is>
+      <c r="N26" s="72" t="s">
+        <v>179</v>
       </c>
       <c r="O26" s="17" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="P26" s="24">
         <v>0.72499999999999998</v>
@@ -4101,48 +3814,48 @@
       <c r="Y26" s="34"/>
       <c r="Z26" s="35"/>
     </row>
-    <row r="27" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A27" s="120" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="121"/>
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="144" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="145"/>
       <c r="C27" s="23"/>
       <c r="D27" s="107">
         <v>0</v>
       </c>
       <c r="E27" s="47">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="F27" s="47">
-        <f>+E27*1.025</f>
+        <f>+E$27*1.025</f>
       </c>
       <c r="G27" s="47">
-        <f>+F27*1.025</f>
+        <f>+F$27*1.025</f>
       </c>
       <c r="H27" s="47">
-        <f>+G27*1.025</f>
+        <f>+G$27*1.025</f>
       </c>
       <c r="I27" s="47">
-        <f>+H27*1.025</f>
+        <f>+H$27*1.025</f>
       </c>
       <c r="J27" s="47">
-        <f>+I27*1.025</f>
+        <f>+I$27*1.025</f>
       </c>
       <c r="K27" s="11"/>
       <c r="L27" s="7"/>
       <c r="N27" t="inlineStr">
         <is>
-          <t xml:space="preserve">ブロック率：1か月目34%（殿村さん）。2か月目以降は前の月×1.025（FMTの式）</t>
+          <t xml:space="preserve">ブロック率：1か月目（E27）から、2か月目以降は前の月×1.025（式）</t>
         </is>
       </c>
       <c r="O27" s="17" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="P27" s="24">
         <v>0.12</v>
       </c>
       <c r="Q27" s="5" t="s">
-        <v>136</v>
+        <v>119</v>
       </c>
       <c r="S27" s="34"/>
       <c r="U27" s="34"/>
@@ -4150,37 +3863,43 @@
       <c r="Y27" s="34"/>
       <c r="Z27" s="35"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A28" s="137" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="138"/>
+    <row r="28" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="146" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="147"/>
       <c r="C28" s="101"/>
       <c r="D28" s="106">
         <v>0</v>
       </c>
       <c r="E28" s="49">
         <f>+D28+E26</f>
+        <v>183.84296875000001</v>
       </c>
       <c r="F28" s="49">
-        <f t="shared" ref="F28:J28" si="8">+E28+F26</f>
+        <f t="shared" ref="F28:J28" si="7">+E28+F26</f>
+        <v>367.68593750000002</v>
       </c>
       <c r="G28" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>551.52890625000009</v>
       </c>
       <c r="H28" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>735.37187500000005</v>
       </c>
       <c r="I28" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>919.21484375</v>
       </c>
       <c r="J28" s="49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
+        <v>1103.0578125</v>
       </c>
       <c r="K28" s="12"/>
       <c r="L28" s="7"/>
       <c r="O28" s="22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="P28" s="77">
         <v>0.2</v>
@@ -4194,37 +3913,44 @@
       <c r="Y28" s="34"/>
       <c r="Z28" s="35"/>
     </row>
-    <row r="29" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A29" s="126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" s="127"/>
+    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" s="148" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="149"/>
       <c r="C29" s="102"/>
       <c r="D29" s="108">
         <f>+D28*(1-D27)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="50">
         <f>+E28*(1-E27)</f>
+        <v>119.4979296875</v>
       </c>
       <c r="F29" s="50">
-        <f t="shared" ref="F29:J29" si="9">+F28*(1-F27)</f>
+        <f t="shared" ref="F29:J29" si="8">+F28*(1-F27)</f>
+        <v>235.77860742187505</v>
       </c>
       <c r="G29" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>337.53569062500003</v>
       </c>
       <c r="H29" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>447.10610000000003</v>
       </c>
       <c r="I29" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>555.20576562500003</v>
       </c>
       <c r="J29" s="50">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
+        <v>661.83468749999997</v>
       </c>
       <c r="K29" s="12"/>
       <c r="L29" s="7"/>
       <c r="N29" s="69" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="S29" s="34"/>
       <c r="U29" s="34"/>
@@ -4232,11 +3958,11 @@
       <c r="Y29" s="34"/>
       <c r="Z29" s="35"/>
     </row>
-    <row r="30" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A30" s="124" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="125"/>
+    <row r="30" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" s="135" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" s="136"/>
       <c r="C30" s="30"/>
       <c r="D30" s="48">
         <v>0</v>
@@ -4261,13 +3987,11 @@
       </c>
       <c r="K30" s="11"/>
       <c r="L30" s="7"/>
-      <c r="N30" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">企画配信 月3回（業界資料のコンサル基本 月20万円は月3投稿。新着求人・職種ごとの案内）</t>
-        </is>
+      <c r="N30" s="69" t="s">
+        <v>181</v>
       </c>
       <c r="O30" s="17" t="s">
-        <v>137</v>
+        <v>120</v>
       </c>
       <c r="P30" s="76"/>
       <c r="S30" s="34"/>
@@ -4276,32 +4000,39 @@
       <c r="Y30" s="34"/>
       <c r="Z30" s="35"/>
     </row>
-    <row r="31" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A31" s="120" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="121"/>
+    <row r="31" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" s="144" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="145"/>
       <c r="C31" s="23"/>
       <c r="D31" s="108">
         <f>+D30*D29*0.41*0.07</f>
+        <v>0</v>
       </c>
       <c r="E31" s="63">
         <f>+E29*E30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>32.75193520974377</v>
       </c>
       <c r="F31" s="63">
         <f>+F29*F30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>64.622087548455994</v>
       </c>
       <c r="G31" s="63">
         <f>+G29*G30*$P$24*$P$22*$P$23*$P$36</f>
+        <v>92.511620069368561</v>
       </c>
       <c r="H31" s="63">
         <f>+H29*H30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>98.034100221657653</v>
       </c>
       <c r="I31" s="63">
         <f>+I29*I30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>121.73642379498608</v>
       </c>
       <c r="J31" s="63">
         <f>+J29*J30*$P$24*$P$22*$P$23*$P$36*$Q$24</f>
+        <v>145.11626677548009</v>
       </c>
       <c r="K31" s="11"/>
       <c r="L31" s="7"/>
@@ -4311,11 +4042,11 @@
       <c r="Y31" s="34"/>
       <c r="Z31" s="35"/>
     </row>
-    <row r="32" spans="1:26" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A32" s="124" t="s">
-        <v>31</v>
-      </c>
-      <c r="B32" s="125"/>
+    <row r="32" spans="1:26" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="B32" s="136"/>
       <c r="C32" s="30"/>
       <c r="D32" s="48">
         <v>0</v>
@@ -4340,148 +4071,171 @@
       </c>
       <c r="K32" s="11"/>
       <c r="L32" s="7"/>
-      <c r="N32" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ステップ配信3通（友だち追加の翌日以降。職種ごとに中身を分ける）</t>
-        </is>
+      <c r="N32" s="69" t="s">
+        <v>182</v>
       </c>
       <c r="O32" s="17" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="P32" s="75" t="b">
         <v>1</v>
       </c>
       <c r="Q32" s="73">
         <f>+IF(P32=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
       </c>
       <c r="S32" s="34"/>
       <c r="U32" s="34"/>
       <c r="W32" s="34"/>
       <c r="Z32" s="35"/>
     </row>
-    <row r="33" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A33" s="120" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" s="121"/>
+    <row r="33" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" s="144" t="s">
+        <v>30</v>
+      </c>
+      <c r="B33" s="145"/>
       <c r="C33" s="23"/>
       <c r="D33" s="44">
         <v>0</v>
       </c>
       <c r="E33" s="63">
         <f>+E29*E32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>9.1327511642554722</v>
       </c>
       <c r="F33" s="63">
-        <f t="shared" ref="F33:G33" si="10">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <f t="shared" ref="F33:G33" si="9">+F29*F32*$P$26*$P$27*$P$28*$P$36</f>
+        <v>18.019620566396377</v>
       </c>
       <c r="G33" s="63">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
+        <v>25.796509442420074</v>
       </c>
       <c r="H33" s="63">
         <f>+H29*H32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>27.336431792577617</v>
       </c>
       <c r="I33" s="63">
-        <f t="shared" ref="I33:J33" si="11">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <f t="shared" ref="I33:J33" si="10">+I29*I32*$P$26*$P$27*$P$28*$P$36*$Q$28</f>
+        <v>33.94573355821727</v>
       </c>
       <c r="J33" s="63">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
+        <v>40.465112850855007</v>
       </c>
       <c r="K33" s="11"/>
       <c r="L33" s="7"/>
       <c r="O33" s="17" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="P33" s="75" t="b">
         <v>1</v>
       </c>
       <c r="Q33" s="73">
-        <f t="shared" ref="Q33:Q35" si="12">+IF(P33=TRUE,1.1,0.95)</f>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A34" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="127"/>
+        <f t="shared" ref="Q33:Q35" si="11">+IF(P33=TRUE,1.1,0.95)</f>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" s="148" t="s">
+        <v>25</v>
+      </c>
+      <c r="B34" s="149"/>
       <c r="C34" s="102"/>
       <c r="D34" s="108">
         <f>+D29*D30</f>
+        <v>0</v>
       </c>
       <c r="E34" s="46">
         <f>+E29*E30*$P$24+E29*E32*$P$28</f>
+        <v>358.49378906250001</v>
       </c>
       <c r="F34" s="46">
         <f>+F29*F30*$P$24+F29*F32*$P$28</f>
+        <v>707.33582226562521</v>
       </c>
       <c r="G34" s="46">
         <f>+G29*G30*$P$24+G29*G32*$P$28</f>
+        <v>1012.6070718750002</v>
       </c>
       <c r="H34" s="46">
         <f>+H29*H30*$P$24*$Q$24+H29*H32*$P$28*$Q$28</f>
+        <v>1073.0546400000001</v>
       </c>
       <c r="I34" s="46">
         <f>+I29*I30*$P$24*$Q$24+I29*I32*$P$28*$Q$28</f>
+        <v>1332.4938375000002</v>
       </c>
       <c r="J34" s="46">
         <f>+J29*J30*$P$24*$Q$24+J29*J32*$P$28*$Q$28</f>
+        <v>1588.4032500000001</v>
       </c>
       <c r="K34" s="11"/>
       <c r="L34" s="7"/>
       <c r="O34" s="17" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="P34" s="75" t="b">
         <v>1</v>
       </c>
       <c r="Q34" s="73">
-        <f t="shared" si="12"/>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="19.5" x14ac:dyDescent="0.4">
-      <c r="A35" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="127"/>
+        <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="19" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" s="148" t="s">
+        <v>24</v>
+      </c>
+      <c r="B35" s="149"/>
       <c r="C35" s="102"/>
       <c r="D35" s="109">
         <f>+D31*1.02</f>
+        <v>0</v>
       </c>
       <c r="E35" s="50">
         <f>+E31+E33+1.05*(E31+E33)</f>
+        <v>85.863607066698449</v>
       </c>
       <c r="F35" s="50">
-        <f t="shared" ref="F35:J35" si="13">+F31+F33+1.05*(F31+F33)</f>
+        <f t="shared" ref="F35:J35" si="12">+F31+F33+1.05*(F31+F33)</f>
+        <v>169.41550163544738</v>
       </c>
       <c r="G35" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
+        <v>242.53166549916671</v>
       </c>
       <c r="H35" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
+        <v>257.0095906291823</v>
       </c>
       <c r="I35" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
+        <v>319.1484225740669</v>
       </c>
       <c r="J35" s="50">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
+        <v>380.44182823398694</v>
       </c>
       <c r="K35" s="11"/>
       <c r="L35" s="7"/>
       <c r="O35" s="17" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="P35" s="75" t="b">
         <v>1</v>
       </c>
       <c r="Q35" s="73">
-        <f t="shared" si="12"/>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A36" s="128" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="6">
+        <f t="shared" si="11"/>
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" s="150" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" s="6" t="str">
         <f>+C8</f>
+        <v>応募</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="11">
@@ -4507,25 +4261,26 @@
       </c>
       <c r="K36" s="115">
         <f>SUM(E36:J36)</f>
+        <v>12</v>
       </c>
       <c r="L36" s="7"/>
-      <c r="N36" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募：クリックの0.3〜1.0%前後</t>
-        </is>
+      <c r="N36" s="69" t="s">
+        <v>183</v>
       </c>
       <c r="O36" s="17" t="s">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="P36" s="74">
         <f>1*(Q32*Q33*Q34*Q35)</f>
+        <v>1.4641000000000006</v>
       </c>
       <c r="Q36" s="73"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A37" s="129"/>
-      <c r="B37" s="6">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" s="151"/>
+      <c r="B37" s="6" t="str">
         <f>+C9</f>
+        <v>-</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="11">
@@ -4551,18 +4306,20 @@
       </c>
       <c r="K37" s="115">
         <f>SUM(E37:J37)</f>
+        <v>0</v>
       </c>
       <c r="L37" s="7"/>
       <c r="N37" s="69" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A38" s="128" t="s">
-        <v>10</v>
-      </c>
-      <c r="B38" s="6">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" s="150" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="6" t="str">
         <f>+C10</f>
+        <v>-</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="11">
@@ -4588,19 +4345,21 @@
       </c>
       <c r="K38" s="115">
         <f>SUM(E38:J38)</f>
+        <v>0</v>
       </c>
       <c r="L38" s="7"/>
       <c r="N38" s="69" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="O38" s="21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A39" s="129"/>
-      <c r="B39" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" s="151"/>
+      <c r="B39" s="6" t="str">
         <f>+C11</f>
+        <v>-</v>
       </c>
       <c r="C39" s="6"/>
       <c r="D39" s="11">
@@ -4626,78 +4385,94 @@
       </c>
       <c r="K39" s="115">
         <f>SUM(E39:J39)</f>
+        <v>0</v>
       </c>
       <c r="L39" s="7"/>
       <c r="N39" s="69" t="s">
-        <v>135</v>
+        <v>118</v>
       </c>
       <c r="O39" s="21" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A40" s="122" t="s">
-        <v>54</v>
-      </c>
-      <c r="B40" s="123"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" s="152" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" s="153"/>
       <c r="C40" s="97"/>
       <c r="D40" s="11">
-        <f t="shared" ref="D40:J40" si="14">+SUM(D36:D39)</f>
+        <f t="shared" ref="D40:J40" si="13">+SUM(D36:D39)</f>
+        <v>0</v>
       </c>
       <c r="E40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="F40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>1</v>
       </c>
       <c r="G40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="H40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>2</v>
       </c>
       <c r="I40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="J40" s="10">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
+        <v>3</v>
       </c>
       <c r="K40" s="115">
         <f>SUM(E40:J40)</f>
+        <v>12</v>
       </c>
       <c r="L40" s="7"/>
       <c r="O40" s="17"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B41" s="5" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D41" s="18">
-        <f t="shared" ref="D41" si="15">+IFERROR(D40/D35,0)</f>
+        <f t="shared" ref="D41" si="14">+IFERROR(D40/D35,0)</f>
+        <v>0</v>
       </c>
       <c r="E41" s="18">
         <f>+IFERROR(E40/E35,0)</f>
+        <v>1.1646377716501063E-2</v>
       </c>
       <c r="F41" s="18">
-        <f t="shared" ref="F41:J41" si="16">+IFERROR(F40/F35,0)</f>
+        <f t="shared" ref="F41:J41" si="15">+IFERROR(F40/F35,0)</f>
+        <v>5.9026475756145712E-3</v>
       </c>
       <c r="G41" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
+        <v>8.2463458776968306E-3</v>
       </c>
       <c r="H41" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
+        <v>7.7818107686324954E-3</v>
       </c>
       <c r="I41" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
+        <v>9.4000151271428269E-3</v>
       </c>
       <c r="J41" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
+        <v>7.8855682455475952E-3</v>
       </c>
       <c r="N41" s="69" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.4">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B42" s="29"/>
       <c r="D42" s="18"/>
       <c r="E42" s="116"/>
@@ -4707,262 +4482,314 @@
       <c r="I42" s="116"/>
       <c r="J42" s="116"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="29" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A44" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="B44" s="121"/>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" s="144" t="s">
+        <v>26</v>
+      </c>
+      <c r="B44" s="145"/>
       <c r="C44" s="103"/>
       <c r="D44" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E44" s="31">
         <f>+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F44" s="31">
-        <f t="shared" ref="F44:J44" si="17">+F75*F76</f>
+        <f t="shared" ref="F44:J44" si="16">+F75*F76</f>
+        <v>0</v>
       </c>
       <c r="G44" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="H44" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="I44" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="J44" s="31">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
+        <v>0</v>
       </c>
       <c r="K44" s="11"/>
       <c r="L44" s="7"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A45" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="121"/>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" s="144" t="s">
+        <v>131</v>
+      </c>
+      <c r="B45" s="145"/>
       <c r="C45" s="104">
         <f>+SUM(C65:C72)</f>
+        <v>0</v>
       </c>
       <c r="D45" s="80">
         <f>+SUM(D65:D72)</f>
+        <v>495000</v>
       </c>
       <c r="E45" s="27">
         <f>SUM(E65:E69)+SUM(E71:E72)</f>
+        <v>265000</v>
       </c>
       <c r="F45" s="27">
-        <f t="shared" ref="F45:J45" si="18">SUM(F65:F69)+SUM(F71:F72)</f>
+        <f t="shared" ref="F45:J45" si="17">SUM(F65:F69)+SUM(F71:F72)</f>
+        <v>265000</v>
       </c>
       <c r="G45" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
+        <v>265000</v>
       </c>
       <c r="H45" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
+        <v>265000</v>
       </c>
       <c r="I45" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
+        <v>265000</v>
       </c>
       <c r="J45" s="27">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
+        <v>265000</v>
       </c>
       <c r="K45" s="11"/>
       <c r="L45" s="7"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A46" s="120" t="s">
-        <v>18</v>
-      </c>
-      <c r="B46" s="121"/>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" s="144" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="145"/>
       <c r="C46" s="103"/>
       <c r="D46" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E46" s="28">
-        <f>IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <f t="shared" ref="E46:J46" si="18">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>326.3654868497656</v>
       </c>
       <c r="F46" s="28">
-        <f>IFERROR(SUM(F65:F67)/(F28-E28),"-")</f>
+        <f t="shared" si="18"/>
+        <v>326.3654868497656</v>
       </c>
       <c r="G46" s="28">
-        <f>IFERROR(SUM(G65:G67)/(G28-F28),"-")</f>
+        <f t="shared" si="18"/>
+        <v>326.36548684976549</v>
       </c>
       <c r="H46" s="28">
-        <f>IFERROR(SUM(H65:H67)/(H28-G28),"-")</f>
+        <f t="shared" si="18"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="I46" s="28">
-        <f>IFERROR(SUM(I65:I67)/(I28-H28),"-")</f>
+        <f t="shared" si="18"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="J46" s="28">
-        <f>IFERROR(SUM(J65:J67)/(J28-I28),"-")</f>
+        <f t="shared" si="18"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="K46" s="11"/>
       <c r="L46" s="7"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A47" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="121"/>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" s="144" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="145"/>
       <c r="C47" s="103"/>
       <c r="D47" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E47" s="28">
-        <f t="shared" ref="E47:I47" si="20">+E51/E35</f>
+        <f t="shared" ref="E47:I47" si="19">+E51/E35</f>
+        <v>3086.2900948727815</v>
       </c>
       <c r="F47" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
+        <v>1564.2016075378615</v>
       </c>
       <c r="G47" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
+        <v>1092.64082879483</v>
       </c>
       <c r="H47" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
+        <v>1031.0899268438056</v>
       </c>
       <c r="I47" s="28">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
+        <v>830.33466956428299</v>
       </c>
       <c r="J47" s="28">
         <f>+J51/J35</f>
+        <v>696.5585283567043</v>
       </c>
       <c r="K47" s="11"/>
       <c r="L47" s="7"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.4">
-      <c r="A48" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="B48" s="121"/>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" s="144" t="s">
+        <v>19</v>
+      </c>
+      <c r="B48" s="145"/>
       <c r="C48" s="103"/>
       <c r="D48" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E48" s="32">
-        <f t="shared" ref="E48:J48" si="21">+SUM(E36:E39)/E35</f>
+        <f t="shared" ref="E48:J48" si="20">+SUM(E36:E39)/E35</f>
+        <v>1.1646377716501063E-2</v>
       </c>
       <c r="F48" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
+        <v>5.9026475756145712E-3</v>
       </c>
       <c r="G48" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
+        <v>8.2463458776968306E-3</v>
       </c>
       <c r="H48" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
+        <v>7.7818107686324954E-3</v>
       </c>
       <c r="I48" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
+        <v>9.4000151271428269E-3</v>
       </c>
       <c r="J48" s="32">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
+        <v>7.8855682455475952E-3</v>
       </c>
       <c r="K48" s="11"/>
       <c r="L48" s="7"/>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A49" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="B49" s="123"/>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" s="152" t="s">
+        <v>18</v>
+      </c>
+      <c r="B49" s="153"/>
       <c r="C49" s="105"/>
       <c r="D49" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E49" s="28">
         <f>+IFERROR(E51/SUM(E36:E39),0)</f>
+        <v>265000</v>
       </c>
       <c r="F49" s="28">
-        <f t="shared" ref="F49:J49" si="22">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <f t="shared" ref="F49:J49" si="21">+IFERROR(F51/SUM(F36:F39),0)</f>
+        <v>265000</v>
       </c>
       <c r="G49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
+        <v>132500</v>
       </c>
       <c r="H49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
+        <v>132500</v>
       </c>
       <c r="I49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
+        <v>88333.333333333328</v>
       </c>
       <c r="J49" s="28">
-        <f t="shared" si="22"/>
+        <f t="shared" si="21"/>
+        <v>88333.333333333328</v>
       </c>
       <c r="K49" s="11"/>
       <c r="L49" s="7"/>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A50" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="B50" s="123"/>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" s="152" t="s">
+        <v>115</v>
+      </c>
+      <c r="B50" s="153"/>
       <c r="C50" s="105"/>
       <c r="D50" s="64" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E50" s="65">
         <f>+E36*$D$8+E38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="F50" s="65">
-        <f t="shared" ref="F50:J50" si="23">+F36*$D$8+F38*$D$10</f>
+        <f t="shared" ref="F50:J50" si="22">+F36*$D$8+F38*$D$10</f>
+        <v>0</v>
       </c>
       <c r="G50" s="65">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="H50" s="65">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="I50" s="65">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="J50" s="65">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
+        <v>0</v>
       </c>
       <c r="K50" s="11"/>
       <c r="L50" s="7"/>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A51" s="118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="119"/>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" s="154" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" s="155"/>
       <c r="C51" s="110">
         <f>+C45</f>
+        <v>0</v>
       </c>
       <c r="D51" s="40">
         <f>+D45</f>
+        <v>495000</v>
       </c>
       <c r="E51" s="40">
         <f>SUM(E45,E50)+E44</f>
+        <v>265000</v>
       </c>
       <c r="F51" s="40">
-        <f t="shared" ref="F51:I51" si="24">SUM(F45,F50)+F44</f>
+        <f t="shared" ref="F51:I51" si="23">SUM(F45,F50)+F44</f>
+        <v>265000</v>
       </c>
       <c r="G51" s="40">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
+        <v>265000</v>
       </c>
       <c r="H51" s="40">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
+        <v>265000</v>
       </c>
       <c r="I51" s="40">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
+        <v>265000</v>
       </c>
       <c r="J51" s="40">
         <f>SUM(J45,J50)+J44</f>
+        <v>265000</v>
       </c>
       <c r="K51" s="11"/>
       <c r="L51" s="7"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="22"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -4974,194 +4801,232 @@
       <c r="I52" s="37"/>
       <c r="J52" s="37"/>
     </row>
-    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A54" s="120" t="s">
-        <v>28</v>
-      </c>
-      <c r="B54" s="121"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" s="144" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="145"/>
       <c r="C54" s="96"/>
       <c r="D54" s="28">
         <f>+D75*D76</f>
+        <v>0</v>
       </c>
       <c r="E54" s="28">
-        <f t="shared" ref="E54:J54" si="25">+E75*E76</f>
+        <f t="shared" ref="E54:J54" si="24">+E75*E76</f>
+        <v>0</v>
       </c>
       <c r="F54" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="G54" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="H54" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="I54" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="J54" s="28">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="K54" s="11"/>
       <c r="L54" s="7"/>
     </row>
-    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="120" t="s">
-        <v>156</v>
-      </c>
-      <c r="B55" s="121"/>
+    <row r="55" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" s="144" t="s">
+        <v>131</v>
+      </c>
+      <c r="B55" s="145"/>
       <c r="C55" s="96"/>
       <c r="D55" s="27">
         <f>+SUM(D65:D72)</f>
+        <v>495000</v>
       </c>
       <c r="E55" s="27">
         <f>SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F55" s="27">
-        <f t="shared" ref="F55:J55" si="26">SUM(F65:F72)+F54</f>
+        <f t="shared" ref="F55:J55" si="25">SUM(F65:F72)+F54</f>
+        <v>265000</v>
       </c>
       <c r="G55" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
+        <v>265000</v>
       </c>
       <c r="H55" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
+        <v>265000</v>
       </c>
       <c r="I55" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
+        <v>265000</v>
       </c>
       <c r="J55" s="27">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
+        <v>265000</v>
       </c>
       <c r="K55" s="11"/>
       <c r="L55" s="7"/>
     </row>
-    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A56" s="120" t="s">
-        <v>18</v>
-      </c>
-      <c r="B56" s="121"/>
+    <row r="56" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" s="144" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" s="145"/>
       <c r="C56" s="96"/>
       <c r="D56" s="39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E56" s="28">
-        <f>IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <f t="shared" ref="E56:J56" si="26">IFERROR(SUM(E65:E67)/(E28-D28),"-")</f>
+        <v>326.3654868497656</v>
       </c>
       <c r="F56" s="28">
-        <f>IFERROR(SUM(F65:F67)/(F28-E28),"-")</f>
+        <f t="shared" si="26"/>
+        <v>326.3654868497656</v>
       </c>
       <c r="G56" s="28">
-        <f>IFERROR(SUM(G65:G67)/(G28-F28),"-")</f>
+        <f t="shared" si="26"/>
+        <v>326.36548684976549</v>
       </c>
       <c r="H56" s="28">
-        <f>IFERROR(SUM(H65:H67)/(H28-G28),"-")</f>
+        <f t="shared" si="26"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="I56" s="28">
-        <f>IFERROR(SUM(I65:I67)/(I28-H28),"-")</f>
+        <f t="shared" si="26"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="J56" s="28">
-        <f>IFERROR(SUM(J65:J67)/(J28-I28),"-")</f>
+        <f t="shared" si="26"/>
+        <v>326.36548684976572</v>
       </c>
       <c r="K56" s="11"/>
       <c r="L56" s="7"/>
     </row>
-    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A57" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="B57" s="121"/>
+    <row r="57" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" s="144" t="s">
+        <v>17</v>
+      </c>
+      <c r="B57" s="145"/>
       <c r="C57" s="96"/>
       <c r="D57" s="39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E57" s="28">
         <f>+E61/E35</f>
+        <v>3086.2900948727815</v>
       </c>
       <c r="F57" s="28">
-        <f t="shared" ref="F57:J57" si="28">+F61/F35</f>
+        <f t="shared" ref="F57:J57" si="27">+F61/F35</f>
+        <v>1564.2016075378615</v>
       </c>
       <c r="G57" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
+        <v>1092.64082879483</v>
       </c>
       <c r="H57" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
+        <v>1031.0899268438056</v>
       </c>
       <c r="I57" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
+        <v>830.33466956428299</v>
       </c>
       <c r="J57" s="28">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
+        <v>696.5585283567043</v>
       </c>
       <c r="K57" s="11"/>
       <c r="L57" s="7"/>
     </row>
-    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A58" s="120" t="s">
-        <v>21</v>
-      </c>
-      <c r="B58" s="121"/>
+    <row r="58" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" s="144" t="s">
+        <v>19</v>
+      </c>
+      <c r="B58" s="145"/>
       <c r="C58" s="96"/>
       <c r="D58" s="39" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E58" s="32">
-        <f t="shared" ref="E58:J58" si="29">+SUM(E36:E39)/E35</f>
+        <f t="shared" ref="E58:J58" si="28">+SUM(E36:E39)/E35</f>
+        <v>1.1646377716501063E-2</v>
       </c>
       <c r="F58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
+        <v>5.9026475756145712E-3</v>
       </c>
       <c r="G58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
+        <v>8.2463458776968306E-3</v>
       </c>
       <c r="H58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
+        <v>7.7818107686324954E-3</v>
       </c>
       <c r="I58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
+        <v>9.4000151271428269E-3</v>
       </c>
       <c r="J58" s="32">
-        <f t="shared" si="29"/>
+        <f t="shared" si="28"/>
+        <v>7.8855682455475952E-3</v>
       </c>
       <c r="K58" s="11"/>
       <c r="L58" s="7"/>
     </row>
-    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A59" s="122" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="123"/>
+    <row r="59" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" s="152" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59" s="153"/>
       <c r="C59" s="97"/>
       <c r="D59" s="28"/>
       <c r="E59" s="28">
         <f>+IFERROR(E55/E40,0)</f>
+        <v>265000</v>
       </c>
       <c r="F59" s="28">
-        <f t="shared" ref="F59:J59" si="30">+IFERROR(F55/F40,0)</f>
+        <f t="shared" ref="F59:J59" si="29">+IFERROR(F55/F40,0)</f>
+        <v>265000</v>
       </c>
       <c r="G59" s="28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
+        <v>132500</v>
       </c>
       <c r="H59" s="28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
+        <v>132500</v>
       </c>
       <c r="I59" s="28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
+        <v>88333.333333333328</v>
       </c>
       <c r="J59" s="28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
+        <v>88333.333333333328</v>
       </c>
       <c r="K59" s="11"/>
       <c r="L59" s="7"/>
     </row>
-    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A60" s="122" t="s">
-        <v>132</v>
-      </c>
-      <c r="B60" s="123"/>
+    <row r="60" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" s="152" t="s">
+        <v>115</v>
+      </c>
+      <c r="B60" s="153"/>
       <c r="C60" s="97"/>
       <c r="D60" s="28"/>
       <c r="E60" s="28"/>
@@ -5173,51 +5038,58 @@
       <c r="K60" s="11"/>
       <c r="L60" s="7"/>
     </row>
-    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.4">
-      <c r="A61" s="118" t="s">
-        <v>71</v>
-      </c>
-      <c r="B61" s="119"/>
+    <row r="61" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" s="154" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="155"/>
       <c r="C61" s="98"/>
       <c r="D61" s="40">
         <f>+D55</f>
+        <v>495000</v>
       </c>
       <c r="E61" s="40">
         <f>+SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F61" s="40">
-        <f t="shared" ref="F61:J61" si="31">+SUM(F65:F72)+F54</f>
+        <f t="shared" ref="F61:J61" si="30">+SUM(F65:F72)+F54</f>
+        <v>265000</v>
       </c>
       <c r="G61" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
+        <v>265000</v>
       </c>
       <c r="H61" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
+        <v>265000</v>
       </c>
       <c r="I61" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
+        <v>265000</v>
       </c>
       <c r="J61" s="40">
-        <f t="shared" si="31"/>
+        <f t="shared" si="30"/>
+        <v>265000</v>
       </c>
       <c r="K61" s="11"/>
       <c r="L61" s="7"/>
     </row>
-    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.4"/>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:12" hidden="1" x14ac:dyDescent="0.55000000000000004"/>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.55000000000000004">
       <c r="C64" s="5" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="52" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C65" s="90">
         <v>0</v>
@@ -5244,14 +5116,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="B66" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ</t>
-        </is>
+        <v>49</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="C66" s="90">
         <v>0</v>
@@ -5277,17 +5147,13 @@
       <c r="J66" s="28">
         <v>30000</v>
       </c>
-      <c r="N66" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">離脱防止ポップアップ：初期1.5万円・月3万円</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.4">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導</t>
-        </is>
+      <c r="N66" s="69" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="C67" s="90">
         <v>0</v>
@@ -5313,16 +5179,14 @@
       <c r="J67" s="28">
         <v>30000</v>
       </c>
-      <c r="N67" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">サンクスLINE誘導：初期15万円・月3万円〜</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.4">
+      <c r="N67" s="69" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="15"/>
       <c r="B68" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C68" s="90">
         <v>0</v>
@@ -5331,41 +5195,43 @@
         <v>30000</v>
       </c>
       <c r="E68" s="28">
-        <f t="shared" ref="E68:J68" si="33">IF(E34&lt;5000,5000,15000)</f>
+        <f t="shared" ref="E68:J68" si="31">IF(E34&lt;5000,5000,15000)</f>
+        <v>5000</v>
       </c>
       <c r="F68" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="G68" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="H68" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="I68" s="28">
-        <f t="shared" si="33"/>
+        <f t="shared" si="31"/>
+        <v>5000</v>
       </c>
       <c r="J68" s="28">
-        <f t="shared" si="33"/>
-      </c>
-      <c r="N68" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">アカウント費：FMTの式（開設3万円）</t>
-        </is>
+        <f t="shared" si="31"/>
+        <v>5000</v>
+      </c>
+      <c r="N68" s="69" t="s">
+        <v>187</v>
       </c>
       <c r="O68" s="17" t="s">
-        <v>154</v>
+        <v>130</v>
       </c>
       <c r="P68" s="75">
         <v>5000</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="15"/>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用コンサル（コンサル基本）</t>
-        </is>
+      <c r="B69" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="C69" s="90">
         <v>0</v>
@@ -5391,19 +5257,17 @@
       <c r="J69" s="28">
         <v>200000</v>
       </c>
-      <c r="N69" s="69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LINE運用コンサル（コンサル基本）月20万円。初期は初期30万円</t>
-        </is>
+      <c r="N69" s="69" t="s">
+        <v>189</v>
       </c>
       <c r="O69" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.4">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="15"/>
       <c r="B70" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C70" s="90">
         <v>0</v>
@@ -5430,13 +5294,13 @@
         <v>0</v>
       </c>
       <c r="N70" s="69" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.4">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="15"/>
       <c r="B71" s="6" t="s">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="C71" s="90">
         <v>0</v>
@@ -5463,13 +5327,13 @@
         <v>0</v>
       </c>
       <c r="N71" s="69" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.4">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="15"/>
       <c r="B72" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C72" s="90">
         <v>0</v>
@@ -5496,37 +5360,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="15"/>
       <c r="B73" s="112" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="C73" s="113">
         <v>0</v>
       </c>
       <c r="D73" s="114">
         <f>SUM(D65:D72)</f>
+        <v>495000</v>
       </c>
       <c r="E73" s="114">
-        <f>SUM(E65:E72)+E54</f>
+        <f t="shared" ref="E73:J73" si="32">SUM(E65:E72)+E54</f>
+        <v>265000</v>
       </c>
       <c r="F73" s="114">
-        <f>SUM(F65:F72)+F54</f>
+        <f t="shared" si="32"/>
+        <v>265000</v>
       </c>
       <c r="G73" s="114">
-        <f>SUM(G65:G72)+G54</f>
+        <f t="shared" si="32"/>
+        <v>265000</v>
       </c>
       <c r="H73" s="114">
-        <f>SUM(H65:H72)+H54</f>
+        <f t="shared" si="32"/>
+        <v>265000</v>
       </c>
       <c r="I73" s="114">
-        <f>SUM(I65:I72)+I54</f>
+        <f t="shared" si="32"/>
+        <v>265000</v>
       </c>
       <c r="J73" s="114">
-        <f>SUM(J65:J72)+J54</f>
-      </c>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.4">
+        <f t="shared" si="32"/>
+        <v>265000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="15"/>
       <c r="B74" s="15"/>
       <c r="C74" s="15"/>
@@ -5538,71 +5409,86 @@
       <c r="I74" s="15"/>
       <c r="J74" s="15"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B75" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D75" s="41">
-        <f t="shared" ref="D75:J75" si="40">+IF(D34&lt;30001,0,D34-30000)</f>
+        <f t="shared" ref="D75:J75" si="33">+IF(D34&lt;30001,0,D34-30000)</f>
+        <v>0</v>
       </c>
       <c r="E75" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="F75" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="G75" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="H75" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="I75" s="41">
-        <f t="shared" si="40"/>
+        <f t="shared" si="33"/>
+        <v>0</v>
       </c>
       <c r="J75" s="41">
-        <f t="shared" si="40"/>
-      </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.4">
+        <f t="shared" si="33"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.55000000000000004">
       <c r="B76" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D76" s="5">
-        <f>+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" ref="D76:J76" si="34">+IF(D75&lt;=$U$18,$Z$18,IF(D75&lt;=$U$19,$Z$19,IF(D75&lt;=$U$20,$Z$20,IF(D75&lt;=$U$21,$Z$21,IF(D75&lt;=$U$22,$Z$22,IF(D75&lt;=$U$23,$Z$23,IF(D75&lt;=$U$24,$Z$24,IF(D75&lt;=$U$25,$Z$25,IF(D75&lt;=$U$26,$Z$26,IF(D75&lt;=$U$27,$Z$27,IF(D75&lt;=$U$28,$Z$28,IF(D75&lt;=$U$29,$Z$29,IF(D75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E76" s="5">
-        <f>+IF(E75&lt;=$U$18,$Z$18,IF(E75&lt;=$U$19,$Z$19,IF(E75&lt;=$U$20,$Z$20,IF(E75&lt;=$U$21,$Z$21,IF(E75&lt;=$U$22,$Z$22,IF(E75&lt;=$U$23,$Z$23,IF(E75&lt;=$U$24,$Z$24,IF(E75&lt;=$U$25,$Z$25,IF(E75&lt;=$U$26,$Z$26,IF(E75&lt;=$U$27,$Z$27,IF(E75&lt;=$U$28,$Z$28,IF(E75&lt;=$U$29,$Z$29,IF(E75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="F76" s="5">
-        <f>+IF(F75&lt;=$U$18,$Z$18,IF(F75&lt;=$U$19,$Z$19,IF(F75&lt;=$U$20,$Z$20,IF(F75&lt;=$U$21,$Z$21,IF(F75&lt;=$U$22,$Z$22,IF(F75&lt;=$U$23,$Z$23,IF(F75&lt;=$U$24,$Z$24,IF(F75&lt;=$U$25,$Z$25,IF(F75&lt;=$U$26,$Z$26,IF(F75&lt;=$U$27,$Z$27,IF(F75&lt;=$U$28,$Z$28,IF(F75&lt;=$U$29,$Z$29,IF(F75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="G76" s="5">
-        <f>+IF(G75&lt;=$U$18,$Z$18,IF(G75&lt;=$U$19,$Z$19,IF(G75&lt;=$U$20,$Z$20,IF(G75&lt;=$U$21,$Z$21,IF(G75&lt;=$U$22,$Z$22,IF(G75&lt;=$U$23,$Z$23,IF(G75&lt;=$U$24,$Z$24,IF(G75&lt;=$U$25,$Z$25,IF(G75&lt;=$U$26,$Z$26,IF(G75&lt;=$U$27,$Z$27,IF(G75&lt;=$U$28,$Z$28,IF(G75&lt;=$U$29,$Z$29,IF(G75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="H76" s="5">
-        <f>+IF(H75&lt;=$U$18,$Z$18,IF(H75&lt;=$U$19,$Z$19,IF(H75&lt;=$U$20,$Z$20,IF(H75&lt;=$U$21,$Z$21,IF(H75&lt;=$U$22,$Z$22,IF(H75&lt;=$U$23,$Z$23,IF(H75&lt;=$U$24,$Z$24,IF(H75&lt;=$U$25,$Z$25,IF(H75&lt;=$U$26,$Z$26,IF(H75&lt;=$U$27,$Z$27,IF(H75&lt;=$U$28,$Z$28,IF(H75&lt;=$U$29,$Z$29,IF(H75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="I76" s="5">
-        <f>+IF(I75&lt;=$U$18,$Z$18,IF(I75&lt;=$U$19,$Z$19,IF(I75&lt;=$U$20,$Z$20,IF(I75&lt;=$U$21,$Z$21,IF(I75&lt;=$U$22,$Z$22,IF(I75&lt;=$U$23,$Z$23,IF(I75&lt;=$U$24,$Z$24,IF(I75&lt;=$U$25,$Z$25,IF(I75&lt;=$U$26,$Z$26,IF(I75&lt;=$U$27,$Z$27,IF(I75&lt;=$U$28,$Z$28,IF(I75&lt;=$U$29,$Z$29,IF(I75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
       <c r="J76" s="5">
-        <f>+IF(J75&lt;=$U$18,$Z$18,IF(J75&lt;=$U$19,$Z$19,IF(J75&lt;=$U$20,$Z$20,IF(J75&lt;=$U$21,$Z$21,IF(J75&lt;=$U$22,$Z$22,IF(J75&lt;=$U$23,$Z$23,IF(J75&lt;=$U$24,$Z$24,IF(J75&lt;=$U$25,$Z$25,IF(J75&lt;=$U$26,$Z$26,IF(J75&lt;=$U$27,$Z$27,IF(J75&lt;=$U$28,$Z$28,IF(J75&lt;=$U$29,$Z$29,IF(J75&lt;=$U$30,$Z$30,0)))))))))))))</f>
+        <f t="shared" si="34"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="A22:A25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A61:B61"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A60:B60"/>
     <mergeCell ref="A47:B47"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
@@ -5615,18 +5501,17 @@
     <mergeCell ref="A44:B44"/>
     <mergeCell ref="A45:B45"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A61:B61"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5636,123 +5521,138 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{024ED691-14F5-4A8E-893C-B7BE5E9344BB}">
   <dimension ref="A1:Y35"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.5" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="41.75" style="29" customWidth="1"/>
     <col min="2" max="2" width="3" style="5" customWidth="1"/>
-    <col min="3" max="6" width="26.125" style="5" customWidth="1"/>
+    <col min="3" max="6" width="26.08203125" style="5" customWidth="1"/>
     <col min="7" max="17" width="9" style="5"/>
-    <col min="18" max="18" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.83203125" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9" style="5"/>
-    <col min="20" max="27" width="14.875" style="5" customWidth="1"/>
+    <col min="20" max="27" width="14.83203125" style="5" customWidth="1"/>
     <col min="28" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="E1" s="81" t="s">
-        <v>171</v>
+        <v>144</v>
       </c>
       <c r="F1" s="81">
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="82" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B3" s="82"/>
       <c r="C3" s="83" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="D3" s="84" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E3" s="84" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F3" s="84"/>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="85" t="s">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="B4" s="7"/>
-      <c r="C4" s="86">
-        <f>+'SIM_コンサル基本'!D24</f>
+      <c r="C4" s="86" t="str">
+        <f>+'SIM_竹（コンサル基本）'!D24</f>
+        <v>--</v>
       </c>
       <c r="D4" s="28">
-        <f>+'SIM_コンサル基本'!G51</f>
+        <f>+'SIM_竹（コンサル基本）'!G51</f>
+        <v>265000</v>
       </c>
       <c r="E4" s="28">
-        <f>+'SIM_コンサル基本'!J51</f>
+        <f>+'SIM_竹（コンサル基本）'!J51</f>
+        <v>265000</v>
       </c>
       <c r="F4" s="28"/>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="85" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="B5" s="7"/>
-      <c r="C5" s="86">
-        <f>+'SIM_コンサル基本'!D25</f>
+      <c r="C5" s="86" t="str">
+        <f>+'SIM_竹（コンサル基本）'!D25</f>
+        <v>--</v>
       </c>
       <c r="D5" s="28">
-        <f>+'SIM_コンサル基本'!G61</f>
+        <f>+'SIM_竹（コンサル基本）'!G61</f>
+        <v>265000</v>
       </c>
       <c r="E5" s="28">
-        <f>+'SIM_コンサル基本'!J61</f>
+        <f>+'SIM_竹（コンサル基本）'!J61</f>
+        <v>265000</v>
       </c>
       <c r="F5" s="27"/>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="85" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="B6" s="7"/>
       <c r="C6" s="117">
-        <f>+'SIM_コンサル基本'!D28</f>
+        <f>+'SIM_竹（コンサル基本）'!D28</f>
+        <v>0</v>
       </c>
       <c r="D6" s="87">
-        <f>+'SIM_コンサル基本'!G28</f>
+        <f>+'SIM_竹（コンサル基本）'!G28</f>
+        <v>551.52890625000009</v>
       </c>
       <c r="E6" s="87">
-        <f>+'SIM_コンサル基本'!J28</f>
+        <f>+'SIM_竹（コンサル基本）'!J28</f>
+        <v>1103.0578125</v>
       </c>
       <c r="F6" s="10"/>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="85" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="B7" s="7"/>
       <c r="C7" s="88">
-        <f>+'SIM_コンサル基本'!D27</f>
+        <f>+'SIM_竹（コンサル基本）'!D27</f>
+        <v>0</v>
       </c>
       <c r="D7" s="89">
-        <f>+'SIM_コンサル基本'!G27</f>
+        <f>+'SIM_竹（コンサル基本）'!G27</f>
+        <v>0.38800000000000001</v>
       </c>
       <c r="E7" s="89">
-        <f>+'SIM_コンサル基本'!J27</f>
+        <f>+'SIM_竹（コンサル基本）'!J27</f>
+        <v>0.4</v>
       </c>
       <c r="F7" s="89"/>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="85" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="117">
-        <f>+'SIM_コンサル基本'!D29</f>
+        <f>+'SIM_竹（コンサル基本）'!D29</f>
+        <v>0</v>
       </c>
       <c r="D8" s="10">
-        <f>+'SIM_コンサル基本'!G29</f>
+        <f>+'SIM_竹（コンサル基本）'!G29</f>
+        <v>337.53569062500003</v>
       </c>
       <c r="E8" s="10">
-        <f>+'SIM_コンサル基本'!J29</f>
+        <f>+'SIM_竹（コンサル基本）'!J29</f>
+        <v>661.83468749999997</v>
       </c>
       <c r="F8" s="10"/>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="85"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -5760,71 +5660,83 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="85" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B10" s="7"/>
       <c r="C10" s="117">
-        <f>+'SIM_コンサル基本'!D34</f>
+        <f>+'SIM_竹（コンサル基本）'!D34</f>
+        <v>0</v>
       </c>
       <c r="D10" s="10">
-        <f>+'SIM_コンサル基本'!G34</f>
+        <f>+'SIM_竹（コンサル基本）'!G34</f>
+        <v>1012.6070718750002</v>
       </c>
       <c r="E10" s="10">
-        <f>+'SIM_コンサル基本'!J34</f>
+        <f>+'SIM_竹（コンサル基本）'!J34</f>
+        <v>1588.4032500000001</v>
       </c>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="85" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B11" s="7"/>
       <c r="C11" s="117">
-        <f>+'SIM_コンサル基本'!D35</f>
+        <f>+'SIM_竹（コンサル基本）'!D35</f>
+        <v>0</v>
       </c>
       <c r="D11" s="10">
-        <f>+'SIM_コンサル基本'!G35</f>
+        <f>+'SIM_竹（コンサル基本）'!G35</f>
+        <v>242.53166549916671</v>
       </c>
       <c r="E11" s="10">
-        <f>+'SIM_コンサル基本'!J35</f>
+        <f>+'SIM_竹（コンサル基本）'!J35</f>
+        <v>380.44182823398694</v>
       </c>
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="85" t="s">
-        <v>174</v>
+        <v>146</v>
       </c>
       <c r="B12" s="7"/>
       <c r="C12" s="28">
         <f>+IFERROR(C5/C11,0)</f>
+        <v>0</v>
       </c>
       <c r="D12" s="28">
         <f>+D4/D11</f>
+        <v>1092.64082879483</v>
       </c>
       <c r="E12" s="28">
         <f t="shared" ref="E12" si="0">+E4/E11</f>
+        <v>696.5585283567043</v>
       </c>
       <c r="F12" s="28"/>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="85" t="s">
-        <v>175</v>
+        <v>147</v>
       </c>
       <c r="B13" s="7"/>
       <c r="C13" s="28">
         <f>+IFERROR(C6/C12,0)</f>
+        <v>0</v>
       </c>
       <c r="D13" s="28">
         <f>+D5/D11</f>
+        <v>1092.64082879483</v>
       </c>
       <c r="E13" s="28">
         <f t="shared" ref="E13" si="1">+E5/E11</f>
+        <v>696.5585283567043</v>
       </c>
       <c r="F13" s="28"/>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="85"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -5832,79 +5744,82 @@
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
       <c r="R14" s="29" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A15" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">応募（サイト・仮に）</t>
-        </is>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="85" t="s">
+        <v>167</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="87">
-        <f>+'SIM_コンサル基本'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <v>134</v>
       </c>
       <c r="D15" s="87">
-        <f>+'SIM_コンサル基本'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <v>134</v>
       </c>
       <c r="E15" s="87">
-        <f>+'SIM_コンサル基本'!$H$10</f>
+        <f>+'SIM_竹（コンサル基本）'!$H$10</f>
+        <v>134</v>
       </c>
       <c r="F15" s="87"/>
       <c r="R15" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A16" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV数（+LINEOA施策）</t>
-        </is>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="85" t="s">
+        <v>190</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="87">
         <f>SUM(C17:C20)</f>
+        <v>0</v>
       </c>
       <c r="D16" s="87">
         <f>SUM(D17:D20)</f>
+        <v>2</v>
       </c>
       <c r="E16" s="87">
         <f>SUM(E17:E20)</f>
+        <v>3</v>
       </c>
       <c r="F16" s="87"/>
       <c r="R16" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="V16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y16" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="V16" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y16" s="35" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A17" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CV①_応募</t>
-        </is>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="85" t="s">
+        <v>191</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="87">
-        <f>+'SIM_コンサル基本'!D36</f>
+        <f>+'SIM_竹（コンサル基本）'!D36</f>
+        <v>0</v>
       </c>
       <c r="D17" s="87">
-        <f>+'SIM_コンサル基本'!G36</f>
+        <f>+'SIM_竹（コンサル基本）'!G36</f>
+        <v>2</v>
       </c>
       <c r="E17" s="87">
-        <f>+'SIM_コンサル基本'!J36</f>
+        <f>+'SIM_竹（コンサル基本）'!J36</f>
+        <v>3</v>
       </c>
       <c r="F17" s="10"/>
       <c r="R17" s="5">
         <v>0</v>
       </c>
       <c r="S17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T17" s="34">
         <v>200000</v>
@@ -5913,7 +5828,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="X17" s="34">
         <v>600000</v>
@@ -5922,28 +5837,29 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A18" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="85" t="s">
+        <v>61</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="87">
-        <f>+'SIM_コンサル基本'!D37</f>
+        <f>+'SIM_竹（コンサル基本）'!D37</f>
+        <v>0</v>
       </c>
       <c r="D18" s="87">
-        <f>+'SIM_コンサル基本'!G37</f>
+        <f>+'SIM_竹（コンサル基本）'!G37</f>
+        <v>0</v>
       </c>
       <c r="E18" s="87">
-        <f>+'SIM_コンサル基本'!J37</f>
+        <f>+'SIM_竹（コンサル基本）'!J37</f>
+        <v>0</v>
       </c>
       <c r="F18" s="10"/>
       <c r="R18" s="34">
         <v>200000</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="T18" s="34">
         <v>15000000</v>
@@ -5952,30 +5868,32 @@
         <v>600000</v>
       </c>
       <c r="W18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="X18" s="34">
         <f>+T18*2.5</f>
+        <v>37500000</v>
       </c>
       <c r="Y18" s="35">
         <v>2.5</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A19" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="85" t="s">
+        <v>61</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="87">
-        <f>+'SIM_コンサル基本'!D38</f>
+        <f>+'SIM_竹（コンサル基本）'!D38</f>
+        <v>0</v>
       </c>
       <c r="D19" s="87">
-        <f>+'SIM_コンサル基本'!G38</f>
+        <f>+'SIM_竹（コンサル基本）'!G38</f>
+        <v>0</v>
       </c>
       <c r="E19" s="87">
-        <f>+'SIM_コンサル基本'!J38</f>
+        <f>+'SIM_竹（コンサル基本）'!J38</f>
+        <v>0</v>
       </c>
       <c r="F19" s="10"/>
       <c r="R19" s="34"/>
@@ -5984,21 +5902,22 @@
       <c r="X19" s="34"/>
       <c r="Y19" s="35"/>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.4">
-      <c r="A20" s="85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">-</t>
-        </is>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="85" t="s">
+        <v>61</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="87">
-        <f>+'SIM_コンサル基本'!D39</f>
+        <f>+'SIM_竹（コンサル基本）'!D39</f>
+        <v>0</v>
       </c>
       <c r="D20" s="87">
-        <f>+'SIM_コンサル基本'!G39</f>
+        <f>+'SIM_竹（コンサル基本）'!G39</f>
+        <v>0</v>
       </c>
       <c r="E20" s="87">
-        <f>+'SIM_コンサル基本'!J39</f>
+        <f>+'SIM_竹（コンサル基本）'!J39</f>
+        <v>0</v>
       </c>
       <c r="F20" s="10"/>
       <c r="R20" s="34"/>
@@ -6007,7 +5926,7 @@
       <c r="X20" s="34"/>
       <c r="Y20" s="35"/>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="85"/>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -6020,19 +5939,22 @@
       <c r="X21" s="34"/>
       <c r="Y21" s="35"/>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="85" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="B22" s="7"/>
-      <c r="C22" s="90">
+      <c r="C22" s="90" t="str">
         <f>+IFERROR(C4/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D22" s="90">
         <f t="shared" ref="D22:E22" si="2">+IFERROR(D4/D16,"--")</f>
+        <v>132500</v>
       </c>
       <c r="E22" s="90">
         <f t="shared" si="2"/>
+        <v>88333.333333333328</v>
       </c>
       <c r="F22" s="90"/>
       <c r="R22" s="34"/>
@@ -6041,19 +5963,22 @@
       <c r="X22" s="34"/>
       <c r="Y22" s="35"/>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="85" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="B23" s="7"/>
-      <c r="C23" s="90">
+      <c r="C23" s="90" t="str">
         <f>+IFERROR(C5/C16,"--")</f>
+        <v>--</v>
       </c>
       <c r="D23" s="90">
         <f t="shared" ref="D23" si="3">+IFERROR(D5/D16,"--")</f>
+        <v>132500</v>
       </c>
       <c r="E23" s="90">
         <f t="shared" ref="E23" si="4">+IFERROR(E5/E16,"--")</f>
+        <v>88333.333333333328</v>
       </c>
       <c r="F23" s="90"/>
       <c r="R23" s="34"/>
@@ -6062,7 +5987,7 @@
       <c r="X23" s="34"/>
       <c r="Y23" s="35"/>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="85"/>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -6075,19 +6000,22 @@
       <c r="X24" s="34"/>
       <c r="Y24" s="35"/>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="85" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="10">
-        <f>+'SIM_コンサル基本'!E68+C29*C30</f>
+        <f>+'SIM_竹（コンサル基本）'!E68+C29*C30</f>
+        <v>5000</v>
       </c>
       <c r="D25" s="10">
-        <f>+'SIM_コンサル基本'!G68+D29*D30</f>
+        <f>+'SIM_竹（コンサル基本）'!G68+D29*D30</f>
+        <v>5000</v>
       </c>
       <c r="E25" s="10">
-        <f>+'SIM_コンサル基本'!J68+E29*E30</f>
+        <f>+'SIM_竹（コンサル基本）'!J68+E29*E30</f>
+        <v>5000</v>
       </c>
       <c r="F25" s="10"/>
       <c r="R25" s="34"/>
@@ -6096,39 +6024,42 @@
       <c r="X25" s="34"/>
       <c r="Y25" s="35"/>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="R26" s="34"/>
       <c r="T26" s="34"/>
       <c r="V26" s="34"/>
       <c r="X26" s="34"/>
       <c r="Y26" s="35"/>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="R27" s="34"/>
       <c r="T27" s="34"/>
       <c r="V27" s="34"/>
       <c r="X27" s="34"/>
       <c r="Y27" s="35"/>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="R28" s="34"/>
       <c r="T28" s="34"/>
       <c r="V28" s="34"/>
       <c r="X28" s="34"/>
       <c r="Y28" s="35"/>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="29" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C29" s="5">
         <f>+IF(C10&lt;=30000,0,C10-30000)</f>
+        <v>0</v>
       </c>
       <c r="D29" s="91">
         <f>+IF(D10&lt;=30000,0,D10-30000)</f>
+        <v>0</v>
       </c>
       <c r="E29" s="91">
         <f>+IF(E10&lt;=30000,0,E10-30000)</f>
+        <v>0</v>
       </c>
       <c r="F29" s="91"/>
       <c r="R29" s="34"/>
@@ -6137,18 +6068,21 @@
       <c r="X29" s="34"/>
       <c r="Y29" s="35"/>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="29" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="C30" s="5">
         <f>+IF(C29&lt;=$T$17,$Y$17,IF(C29&lt;=$T$18,$Y$18,IF(C29&lt;=$T$19,$Y$19,IF(C29&lt;=$T$20,$Y$20,IF(C29&lt;=$T$21,$Y$21,IF(C29&lt;=$T$22,$Y$22,IF(C29&lt;=$T$23,$Y$23,IF(C29&lt;=$T$24,$Y$24,IF(C29&lt;=$T$25,$Y$25,IF(C29&lt;=$T$26,$Y$26,IF(C29&lt;=$T$27,$Y$27,IF(C29&lt;=$T$28,$Y$28,IF(C29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="D30" s="5">
         <f>+IF(D29&lt;=$T$17,$Y$17,IF(D29&lt;=$T$18,$Y$18,IF(D29&lt;=$T$19,$Y$19,IF(D29&lt;=$T$20,$Y$20,IF(D29&lt;=$T$21,$Y$21,IF(D29&lt;=$T$22,$Y$22,IF(D29&lt;=$T$23,$Y$23,IF(D29&lt;=$T$24,$Y$24,IF(D29&lt;=$T$25,$Y$25,IF(D29&lt;=$T$26,$Y$26,IF(D29&lt;=$T$27,$Y$27,IF(D29&lt;=$T$28,$Y$28,IF(D29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="E30" s="5">
         <f>+IF(E29&lt;=$T$17,$Y$17,IF(E29&lt;=$T$18,$Y$18,IF(E29&lt;=$T$19,$Y$19,IF(E29&lt;=$T$20,$Y$20,IF(E29&lt;=$T$21,$Y$21,IF(E29&lt;=$T$22,$Y$22,IF(E29&lt;=$T$23,$Y$23,IF(E29&lt;=$T$24,$Y$24,IF(E29&lt;=$T$25,$Y$25,IF(E29&lt;=$T$26,$Y$26,IF(E29&lt;=$T$27,$Y$27,IF(E29&lt;=$T$28,$Y$28,IF(E29&lt;=$T$29,$Y$29,0)))))))))))))</f>
+        <v>3</v>
       </c>
       <c r="R30" s="34"/>
       <c r="T30" s="34"/>
@@ -6156,28 +6090,28 @@
       <c r="X30" s="34"/>
       <c r="Y30" s="35"/>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.55000000000000004">
       <c r="R31" s="34"/>
       <c r="T31" s="34"/>
       <c r="V31" s="34"/>
       <c r="Y31" s="35"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="92" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="B35" s="92"/>
       <c r="C35" s="93" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="D35" s="94" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="E35" s="94" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
       <c r="F35" s="94" t="s">
-        <v>165</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -6189,15 +6123,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1CA14B7-1E76-4B86-9C33-BD8F21953694}">
   <dimension ref="A2:J42"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="14.25" customWidth="1"/>
     <col min="5" max="5" width="14.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="59" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B2" s="59"/>
       <c r="C2" s="59"/>
@@ -6206,197 +6140,201 @@
       <c r="F2" s="59"/>
       <c r="G2" s="59"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="54" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E4">
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5" s="60">
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B6" s="60">
         <v>0.08</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="E7">
         <f>+E4*B5*B6</f>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>6.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="54" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E9">
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B10" s="60">
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B11" s="60">
         <v>0.08</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="E12">
         <f>+E9*B10*B11</f>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="54" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E14">
         <v>1000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B15" s="60">
         <v>0.9</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B16" s="60">
         <v>0.35</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="E17">
         <f>+E14*B15*B16</f>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="54" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B19" s="60">
         <v>0.7</v>
       </c>
       <c r="C19" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="E19">
         <v>1000</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" s="60">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B21" s="60">
         <v>0.2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="E22">
         <f>+E19*B20*B21</f>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="59" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B23" s="59"/>
       <c r="C23" s="59" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D23" s="59"/>
       <c r="E23" s="59"/>
       <c r="F23" s="59"/>
       <c r="G23" s="59"/>
       <c r="I23" s="67" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="J23" s="68"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="54" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="I24" s="66">
         <v>1</v>
       </c>
       <c r="J24" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B25" s="61">
         <v>0.8</v>
@@ -6405,12 +6343,12 @@
         <v>2</v>
       </c>
       <c r="J25" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B26" s="61">
         <v>0.06</v>
@@ -6419,12 +6357,12 @@
         <v>3</v>
       </c>
       <c r="J26" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B27" s="61">
         <v>3.0000000000000001E-3</v>
@@ -6433,21 +6371,21 @@
         <v>4</v>
       </c>
       <c r="J27" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="54" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="I29" s="67" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="J29" s="68"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B30" s="61">
         <v>0.75</v>
@@ -6456,12 +6394,12 @@
         <v>1</v>
       </c>
       <c r="J30" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B31" s="61">
         <v>0.08</v>
@@ -6470,12 +6408,12 @@
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B32" s="61">
         <v>6.0000000000000001E-3</v>
@@ -6484,85 +6422,85 @@
         <v>3</v>
       </c>
       <c r="J32" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="I33" s="66">
         <v>4</v>
       </c>
       <c r="J33" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="54" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" s="62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" s="61">
         <v>0.02</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B37" s="61">
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="54" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="E39" s="54" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B40" s="62">
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F40" s="62" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B41" s="61">
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="F41" s="61">
         <v>0.25</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B42" s="61">
         <v>6.0000000000000001E-3</v>
@@ -6576,23 +6514,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100C357D3FFD3874644B9B63D306D91E343" ma:contentTypeVersion="5" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="bfcf90751a1be541a10eb2cf2bfdf12b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="79deb97c-193b-473b-ac92-dc976e68b6a4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9df8bde209fb52400f7491d2ba74e6ee" ns3:_="">
     <xsd:import namespace="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
@@ -6742,31 +6663,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="79deb97c-193b-473b-ac92-dc976e68b6a4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2519B170-E350-4E75-B7A7-F72CE5062C7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6782,4 +6696,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2CA9CD83-13A7-4B09-B9AB-AAF5EBC76B43}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{010C7DA8-EA1E-4EA4-BD5C-CCDDE9E9CCA3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="79deb97c-193b-473b-ac92-dc976e68b6a4"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>